--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,413 +656,425 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44562</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44198</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43827</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43463</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43099</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1614100</v>
+      </c>
+      <c r="E8" s="3">
         <v>1625200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1757600</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1791200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1768100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1747600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1650200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1366300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1310100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1185900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1198700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1046700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1019800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>850600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>848700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>852800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>859400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>842000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>827300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>835100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>853100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>812600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>846600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>875400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>952500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>936300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>894900</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>878500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>881100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1177700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1238700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1359700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1367000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1379300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1371200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1231500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1020600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>988900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>859600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>878100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>772800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>768600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>637500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>633800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>649600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>640100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>656000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>643000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>648000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>667600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>649200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>654100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>678200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>688400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>436400</v>
+      </c>
+      <c r="E10" s="3">
         <v>386500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>397900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>424200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>388800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>376400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>418700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>345700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>321200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>326300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>320600</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>273900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>251200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>213100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>214900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>203200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>219300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>186000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>184300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>187100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>185500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>163400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>192500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>197200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>192700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,8 +1107,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1200,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,86 +1295,89 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E14" s="3">
         <v>3400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>11500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>23800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>4500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>13900</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>3800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>1400</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
         <v>0</v>
       </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>38200</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3000</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>12100</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>54000</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
         <v>0</v>
       </c>
@@ -1371,100 +1390,106 @@
       <c r="AF14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>137900</v>
+      </c>
+      <c r="E15" s="3">
         <v>126000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>122100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>116000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>117400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>105000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>93100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>79200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>80800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>77800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>79200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>78500</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>96500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>85700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>83300</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>84700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>86500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>80400</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>79500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>79200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>85300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>78800</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>78500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>78600</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>80800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>77200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>73000</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>71100</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>77500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1519,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1455300</v>
+      </c>
+      <c r="E17" s="3">
         <v>1446800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1535300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1518900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1479300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1371600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1133400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1099000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>980300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>930400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>847200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>945500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>723100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>742400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>730000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>563200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>782200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>765300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>810800</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>779400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>794000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>864000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>843600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>917300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>901900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>856800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>846000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>845700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>158800</v>
+      </c>
+      <c r="E18" s="3">
         <v>178400</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>356700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>255900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>249200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>268300</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>278600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>232900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>211100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>205600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>268300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>199500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>74300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>127500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>106300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>122800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>296200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>59800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>62000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>73700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>18600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>31800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>35200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>34400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>38100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>32500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,468 +1744,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E20" s="3">
         <v>4600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>9400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>11300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-5900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-2500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>600</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-900</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>1400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>20500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-3300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>13000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>93100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>9000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>2400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>34900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>300900</v>
+      </c>
+      <c r="E21" s="3">
         <v>309000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>488200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>383100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>360700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>372300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>369300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>311700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>291200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>284100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>347500</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>277100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>169700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>210900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>187700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>208200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>384100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>137500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>139200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>124000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>155700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>92400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>74000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>203500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>125000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>114700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>113500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>102000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>147800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>68500</v>
+      </c>
+      <c r="E22" s="3">
         <v>70300</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>70200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>50300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>46100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>39800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>15600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>16400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>18800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>17900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>19100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>20900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>23000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>22300</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22500</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>22400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>21700</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>94500</v>
+      </c>
+      <c r="E23" s="3">
         <v>112700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>295900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>216800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>197200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>227500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>252200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>216800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>195400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>190800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>253000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>182100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>56400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>106400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>86400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>104400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>279000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>37700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>38800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>24900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>50200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-27500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>101800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>21900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>15000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>18100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9200</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>47900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-15400</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>40700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>38000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>35200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>47300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26100</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>37800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>42600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>55000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>10200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>19900</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>18300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>35600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>7800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>9700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>6300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2312,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>87300</v>
+      </c>
+      <c r="E26" s="3">
         <v>128100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>255200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>189900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>159200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>192300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>204800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>190700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>157600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>148200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>198100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>153400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>46100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>101600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>66500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>86100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>243400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>26800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>31000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>19600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>40400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-29100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>98100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>70200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>8700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>10300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>41700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E27" s="3">
         <v>125000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>252400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>185800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>156600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>191100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>202000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>188100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>155800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>146800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>196600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>151800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>44700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>101100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>65400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>85500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>242600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>25700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>26300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>18000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>38900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>97300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>69000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>40500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,8 +2597,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2584,8 +2644,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2602,11 +2662,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>1700</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2614,11 +2674,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2632,8 +2692,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2787,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,192 +2882,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-4100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-9400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-11300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>5900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>2500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-600</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>900</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-1400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-20500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>3300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E33" s="3">
         <v>125000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>252400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>185800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>156600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>191100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>202000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>188100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>155800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>146800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>196600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>151800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>44700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>101100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>65400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>85500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>242600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>25700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>26300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>18000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>40600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>97300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>105700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3167,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E35" s="3">
         <v>125000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>252400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>185800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>156600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>191100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>202000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>188100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>155800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>146800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>196600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>151800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>44700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>101100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>65400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>85500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>242600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>25700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>26300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>18000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>40600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>97300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>105700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44562</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44198</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43827</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43463</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43099</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3399,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,100 +3434,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>126500</v>
+      </c>
+      <c r="E41" s="3">
         <v>119000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>111500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>132600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>127000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>126000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>146700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>99500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>68900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>67200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>77700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>71200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>81600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>65800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>76200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>72900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>69100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>87000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>95700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>107300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>104100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>122900</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>106800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>110100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>124800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>138900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>114600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3533,652 +3622,676 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>821900</v>
+      </c>
+      <c r="E43" s="3">
         <v>761300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>769300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>770900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>695200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>687300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>602100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>542800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>470200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>482600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>436100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>388900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>409300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>377500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>379700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>400800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>409700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>360000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>363200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>375400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>392200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>371700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>378300</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>418400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>396400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>420300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>389300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>396800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>395900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>758700</v>
+      </c>
+      <c r="E44" s="3">
         <v>822800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>825100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>828800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>673600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>642000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>578400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>491700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>457500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>476300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>428200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>420700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>405900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>406800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>394700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>381400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>363000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>353000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>348300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>339900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>341000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>361700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>370600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>373100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>358200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>375100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>359600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>342100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>330800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E45" s="3">
         <v>140000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>170000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>170300</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>142300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>106700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>134600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>125000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>92500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>77500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>80600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>60000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>90200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>81000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>80500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>71500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>71700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>71600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>68600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>57500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>63700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>65300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>56700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>95100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>56700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>51100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>49500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>52000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1855700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1843000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1876000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1902500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1638100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1562000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1461800</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1259000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1089000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1103600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1022600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>940800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>987000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>931200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>931100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>930100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>917300</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>853700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>867100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>871200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>897900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>878500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>918200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>971100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>956400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>962200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>924900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>927300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>893300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2251600</v>
+      </c>
+      <c r="E47" s="3">
         <v>2164200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2214300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2125100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1926400</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1814600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1736200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1563800</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1349200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1107800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1037400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>915100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>804700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>742900</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>729100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>802200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>689400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>447700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>458000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>433400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>410200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>398800</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>399100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>409100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>302000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>290000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>279800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>270900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>292700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3140700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3001700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2971100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2901800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2648200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2520800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2414500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2033000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1995500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1995300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2011800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1967300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2010400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1931400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1908200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1888000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1927100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1833800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1843200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1821300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1687900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1631000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1624400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3560400</v>
+      </c>
+      <c r="E49" s="3">
         <v>3538800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3640800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3678700</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2835500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2773900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2315900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1646200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1616900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1649600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1684600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1693800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1733900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1714100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1702300</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="S49" s="3">
-        <v>1749700</v>
       </c>
       <c r="T49" s="3">
         <v>1749700</v>
       </c>
       <c r="U49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="V49" s="3">
         <v>1799500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1801700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1825000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1826800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1843800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4382,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,100 +4477,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>252700</v>
+      </c>
+      <c r="E52" s="3">
         <v>262700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>271100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>252900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>154200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>137500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>98200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>113600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>83000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>69300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>76900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>74500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>77400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>61400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>56500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>57200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>61800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>60000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>68700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>67500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>70100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>71400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>78200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>76300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>64200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>65300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>57800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>58600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,100 +4667,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>11061100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10810300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10973200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10861100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>9202400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>8808800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8026700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6615600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6133700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>5925700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5833300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5591400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5613300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5381000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5327200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5377800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5345300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>4944900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5036600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4995100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4889400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4805200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4856900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4799,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,560 +4834,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>425600</v>
+      </c>
+      <c r="E57" s="3">
         <v>394700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>427100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>433800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>472500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>398200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>414600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>351300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>307100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>272800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>264400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>245600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>255300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>207000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>197500</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>211600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>239300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>192000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>208900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>192500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>219500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>177800</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>185200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>188000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>217400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>213600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>186500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>181400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>180900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>60700</v>
+      </c>
+      <c r="E58" s="3">
         <v>73900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>88100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>118800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>69800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>63700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>32700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>35300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>24400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>55100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>41600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>27000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>26200</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>42800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>86400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>91000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>61100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>35900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>23700</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>7500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>11100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>16700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>16100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>18200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>19400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>25000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>511800</v>
+      </c>
+      <c r="E59" s="3">
         <v>565100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>498400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>546400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>526100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>566100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>472500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>426800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>421200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>428200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>386200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>365100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>392400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>390400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>366000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>353800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>358100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>342800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>321500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>330000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>313500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>297000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>290100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>302100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>325900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>314500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>283200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>245400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>247700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>998100</v>
+      </c>
+      <c r="E60" s="3">
         <v>1033700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1013500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1099000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1068400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1028000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>919800</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>813400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>752700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>756200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>692200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>637700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>675300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>623600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>606300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>651700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>688300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>595900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>566300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>546200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>540500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>485800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>482700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>506900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>559500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>546300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>489000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>451800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>451900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4366400</v>
+      </c>
+      <c r="E61" s="3">
         <v>4338100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4458800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4558600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3315000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3220900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2881100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1677900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1439000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1325700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1393800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1417500</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1480500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1448000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1553100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1664900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1558400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1559800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1640100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1663800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1666900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1668100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1687800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1002900</v>
+      </c>
+      <c r="E62" s="3">
         <v>971500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1050300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1081900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>922500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>891100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>659200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>628600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>594300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>574600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>563500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>506300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>503300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>474200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>469400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>452700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>455100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>416300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>423600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>428400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>346100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>335900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>348300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>375000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>373000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>449400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>446100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>436500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>442200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5497,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5592,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,100 +5687,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6455700</v>
+      </c>
+      <c r="E66" s="3">
         <v>6429600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6605000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6828600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5393300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5228600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>4533200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>3190300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2852800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2720200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2714700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2624800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2721400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2607100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2693800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2834200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2779400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2636400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2693700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2704500</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2616300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2550800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2593500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5819,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5912,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6007,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6102,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,100 +6197,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3733300</v>
+      </c>
+      <c r="E72" s="3">
         <v>3648700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3523700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3271300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3085500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2929000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2737900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2535900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2347800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2192100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2045300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1848700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1696900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1652200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1551100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1485600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1400100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1157500</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1131800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1105500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1087500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1046900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1052900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>981200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>875500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>867700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>858600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>852800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6387,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6482,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,100 +6577,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4605400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4380700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4368200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4032500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>3809000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3580100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3493500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3425300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3281000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3205500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3118600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2966600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2891900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2773900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2633400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2543600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2565800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2308500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2342900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2290500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2273000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2254400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2263400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6767,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45290</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44562</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44198</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43827</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43463</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43099</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>84500</v>
+      </c>
+      <c r="E81" s="3">
         <v>125000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>252400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>185800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>156600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>191100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>202000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>188100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>155800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>146800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>196600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>151800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>44700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>101100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>65400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>85500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>242600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>25700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>26300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>18000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>40600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-30400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>97300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>105700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,100 +6999,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>137900</v>
+      </c>
+      <c r="E83" s="3">
         <v>126000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>122100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>116000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>117400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>105000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>93100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>80800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>77800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>78500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>96500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>85700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>83300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>84700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>86500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>80400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>79500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>79200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>85300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>78800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>78500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>78600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>80800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>77200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>73000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>71100</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>77500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7187,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7282,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7377,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7472,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7567,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>217000</v>
+      </c>
+      <c r="E89" s="3">
         <v>276600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>217300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>188400</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>175300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>277400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>208800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>152200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>252400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>154100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>159100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>138800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>154200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>206800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>229100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>34500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>99900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>108400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>105700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>48600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>198900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>71700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>101100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>26900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>141800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>71200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>103100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>94500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>110500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7699,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-174900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-146200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-123000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-111300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-134200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-105600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-79900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-71600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-82400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-65600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-65300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-60800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-95200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="Q91" s="3">
-        <v>-61600</v>
       </c>
       <c r="R91" s="3">
         <v>-61600</v>
       </c>
       <c r="S91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="T91" s="3">
         <v>-114400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-77200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-83600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-84300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-108200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-74600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-82500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7887,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +7982,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-168800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-158300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-193800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-598000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-294500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-270500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-89800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-65600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-64300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-123300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-64600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-103200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-72100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-83000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-79800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-153600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-78200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-55400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8114,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7974,8 +8207,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8302,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8397,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,280 +8492,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-117900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-152700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1172800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>325300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1176700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>180900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>18700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-69200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-89800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-81000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-19500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-159500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-168400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>40400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>5300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-49200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-32100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>21200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-17600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-21300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-54800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>46200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>25600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>1200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>2900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3800</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>4400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>3900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>300</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-4900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-1600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>5100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-9600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>3900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>10900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>10900</v>
+      </c>
+      <c r="E102" s="3">
         <v>9400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-17700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>111700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>47300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>30500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-10600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>15800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>3400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-17800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-8700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-11500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>25800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-22700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-18700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>16100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>24300</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,425 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45290</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44562</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44198</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43827</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43463</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43099</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1420300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1614100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1625200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1757600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1791200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1768100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1747600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1650200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1366300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1310100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1185900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1198700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1046700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1019800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>850600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>848700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>852800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>859400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>842000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>827300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>835100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>853100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>812600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>846600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>875400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>952500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>936300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>894900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>878500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>881100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1116700</v>
+      </c>
+      <c r="E9" s="3">
         <v>1177700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1238700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1359700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1367000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1379300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1371200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1231500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1020600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>988900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>859600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>878100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>772800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>768600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>637500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>633800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>649600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>640100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>656000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>643000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>648000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>667600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>649200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>654100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>678200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>688400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>303600</v>
+      </c>
+      <c r="E10" s="3">
         <v>436400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>386500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>397900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>424200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>388800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>376400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>418700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>345700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>321200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>326300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>320600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>273900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>251200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>213100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>214900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>203200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>219300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>186000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>184300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>187100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>185500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>163400</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>192500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>197200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>192700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1108,8 +1121,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1203,8 +1217,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1298,89 +1315,92 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E14" s="3">
         <v>14900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>3400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>2600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>23800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>4500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>13900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>3800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1400</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
         <v>0</v>
       </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>38200</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
-      <c r="S14" s="3" t="s">
+      <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3000</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>12100</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>54000</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
         <v>0</v>
       </c>
@@ -1393,103 +1413,109 @@
       <c r="AG14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E15" s="3">
         <v>137900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>126000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>122100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>116000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>117400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>105000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>93100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>79200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>80800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>77800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>79200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>78500</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>96500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>85700</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>83300</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>84700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>86500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>80400</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>79500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>79200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>85300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>78800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>78500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>78600</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>80800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>77200</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>73000</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>71100</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>77500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1520,198 +1546,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1283100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1455300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1446800</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1535300</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1518900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1479300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1371600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1133400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1099000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>980300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>930400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>847200</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>945500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>723100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>742400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>730000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>563200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>782200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>765300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>810800</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>779400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>794000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>864000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>843600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>917300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>901900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>856800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>846000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>845700</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>137200</v>
+      </c>
+      <c r="E18" s="3">
         <v>158800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>178400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>356700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>255900</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>249200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>268300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>278600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>232900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>211100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>205600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>268300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>199500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>74300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>127500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>106300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>122800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>296200</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>59800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>62000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>73700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>18600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>31800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>35200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>34400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>38100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>32500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1745,483 +1778,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E20" s="3">
         <v>4100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>9400</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>11300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-5900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-1000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-700</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>600</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>-900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2800</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>20500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>13000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>93100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>9000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2400</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>34900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>275900</v>
+      </c>
+      <c r="E21" s="3">
         <v>300900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>309000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>488200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>383100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>360700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>372300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>369300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>311700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>291200</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>284100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>347500</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>277100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>169700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>210900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>187700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>208200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>384100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>137500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>139200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>124000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>155700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>92400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>74000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>203500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>125000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>114700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>113500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>102000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>147800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>62900</v>
+      </c>
+      <c r="E22" s="3">
         <v>68500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>70300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>70200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>50300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>46100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>39800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>24000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>15600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>16400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>18800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>17900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>19100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>20900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20200</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20100</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>23000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>22300</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>22500</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>21700</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>85500</v>
+      </c>
+      <c r="E23" s="3">
         <v>94500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>112700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>295900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>216800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>197200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>227500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>252200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>216800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>195400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>190800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>253000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>182100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>56400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>106400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>86400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>104400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>279000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>37700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>38800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>24900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>50200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-6500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>101800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>21900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>15000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>18100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>47900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E24" s="3">
         <v>7200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-15400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>40700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>38000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>35200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>47300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>37800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>42600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>55000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>10200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>19900</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>18300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>35600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>7800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>5300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>9700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>6300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2315,198 +2364,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E26" s="3">
         <v>87300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>128100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>255200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>189900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>159200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>192300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>204800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>190700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>157600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>148200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>198100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>153400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>46100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>101600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>66500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>86100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>243400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>26800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>31000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>19600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>40400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-5100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>98100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>70200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>8700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>10300</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>7400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>41700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E27" s="3">
         <v>84500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>125000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>252400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>185800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>156600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>191100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>202000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>188100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>155800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>146800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>196600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>151800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>44700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>101100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>65400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>85500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>242600</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>25700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>26300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>18000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>38900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>97300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>69000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>40500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2600,8 +2658,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2647,8 +2708,8 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2665,11 +2726,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>1700</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2677,11 +2738,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2695,8 +2756,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2790,8 +2854,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2885,198 +2952,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-11200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-4100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-9400</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-11300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>5900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>1000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>700</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-600</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2800</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-20500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>3300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>5100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E33" s="3">
         <v>84500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>125000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>252400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>185800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>156600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>191100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>202000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>188100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>155800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>146800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>196600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>151800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>44700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>101100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>65400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>85500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>242600</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>25700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>26300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>18000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>40600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>97300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>105700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>40500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3170,203 +3246,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E35" s="3">
         <v>84500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>125000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>252400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>185800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>156600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>191100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>202000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>188100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>155800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>146800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>196600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>151800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>44700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>101100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>65400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>85500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>242600</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>25700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>26300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>18000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>40600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>97300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>105700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>40500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45290</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44562</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44198</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43827</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43463</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43099</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3400,8 +3485,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3435,103 +3521,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>145500</v>
+      </c>
+      <c r="E41" s="3">
         <v>126500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>119000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>111500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>132600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>127000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>126000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>146700</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>99500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>68900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>67200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>77700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>71200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>81600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>65800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>76200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>72900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>69100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>87000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>95700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>107300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>81500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>104100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>122900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>106800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>110100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>124800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>138900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>114600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3625,673 +3715,697 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>656400</v>
+      </c>
+      <c r="E43" s="3">
         <v>821900</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>761300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>769300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>770900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>695200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>687300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>602100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>542800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>470200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>482600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>436100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>388900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>409300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>377500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>379700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>400800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>409700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>360000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>363200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>375400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>392200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>371700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>378300</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>418400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>396400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>420300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>389300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>396800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>395900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>687500</v>
+      </c>
+      <c r="E44" s="3">
         <v>758700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>822800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>825100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>828800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>673600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>642000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>578400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>491700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>457500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>476300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>428200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>420700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>405900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>406800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>394700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>381400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>363000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>353000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>348300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>339900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>341000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>361700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>370600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>373100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>358200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>375100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>359600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>342100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>330800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>130000</v>
+      </c>
+      <c r="E45" s="3">
         <v>148500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>140000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>170000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>170300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>142300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>106700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>134600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>125000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>92500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>77500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>80600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>60000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>90200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>81000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>80500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>71500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>71700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>71600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>68600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>60100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>57500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>63700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>65300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>56700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>95100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>56700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>51100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>49500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>52000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1619300</v>
+      </c>
+      <c r="E46" s="3">
         <v>1855700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1843000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1876000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1902500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1638100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1562000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1461800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1259000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1089000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1103600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1022600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>940800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>987000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>931200</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>931100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>930100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>917300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>853700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>867100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>871200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>897900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>878500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>918200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>971100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>956400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>962200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>924900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>927300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>893300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2378500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2251600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2164200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2214300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2125100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1926400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1814600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1736200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1563800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1349200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1107800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1037400</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>915100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>804700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>742900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>729100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>802200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>689400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>447700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>458000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>433400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>410200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>398800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>399100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>409100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>302000</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>290000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>279800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>270900</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>292700</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3126200</v>
+      </c>
+      <c r="E48" s="3">
         <v>3140700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3001700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2971100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2901800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2648200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2520800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2414500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2033000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1995500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1995300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2011800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1967300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2010400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1931400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1908200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1888000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1927100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1833800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1843200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1821300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1687900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1631000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3555600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3560400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3538800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3640800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3678700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2835500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2773900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2315900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1646200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1616900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1649600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1684600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1693800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1733900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1714100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1702300</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="T49" s="3">
-        <v>1749700</v>
       </c>
       <c r="U49" s="3">
         <v>1749700</v>
       </c>
       <c r="V49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="W49" s="3">
         <v>1799500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1801700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1825000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1826800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4385,8 +4499,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4480,103 +4597,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>263100</v>
+      </c>
+      <c r="E52" s="3">
         <v>252700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>262700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>271100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>252900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>154200</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>137500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>98200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>113600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>83000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>69300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>76900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>74500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>77400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>61400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>56500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>57200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>61800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>60000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>68700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>67500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>70100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>71400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>78200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>76300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>64200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>65300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>57800</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>58600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4670,103 +4793,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10942800</v>
+      </c>
+      <c r="E54" s="3">
         <v>11061100</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10810300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10973200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10861100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>9202400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>8808800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8026700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6615600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6133700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>5925700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5833300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5591400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5613300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5381000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5327200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5377800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5345300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>4944900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5036600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4995100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4889400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4805200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4800,8 +4929,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4835,578 +4965,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>343400</v>
+      </c>
+      <c r="E57" s="3">
         <v>425600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>394700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>427100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>433800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>472500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>398200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>414600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>351300</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>307100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>272800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>264400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>245600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>255300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>207000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>197500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>211600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>239300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>192000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>208900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>192500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>219500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>177800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>185200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>188000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>217400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>213600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>186500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>181400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>180900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>103100</v>
+      </c>
+      <c r="E58" s="3">
         <v>60700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>73900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>88100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>118800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>69800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>63700</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>32700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>35300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>24400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>55100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>41600</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>27000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>26200</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>42800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>86400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>91000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>61100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>35900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>23700</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>7500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>11100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>16700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>18200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>19400</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>25000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>23200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>520800</v>
+      </c>
+      <c r="E59" s="3">
         <v>511800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>565100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>498400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>546400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>526100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>566100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>472500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>426800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>421200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>428200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>386200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>365100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>392400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>390400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>366000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>353800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>358100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>342800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>321500</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>330000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>313500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>297000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>290100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>302100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>325900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>314500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>283200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>245400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>247700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>967300</v>
+      </c>
+      <c r="E60" s="3">
         <v>998100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1033700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1013500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1099000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1068400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1028000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>919800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>813400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>752700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>756200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>692200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>637700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>675300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>623600</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>606300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>651700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>688300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>595900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>566300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>546200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>540500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>485800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>482700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>506900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>559500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>546300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>489000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>451800</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>451900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4362900</v>
+      </c>
+      <c r="E61" s="3">
         <v>4366400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4338100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4458800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4558600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3315000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3220900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2881100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1677900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1439000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1325700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1393800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1417500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1480500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1448000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1553100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1664900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1558400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1559800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1640100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1663800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1666900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1668100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>929600</v>
+      </c>
+      <c r="E62" s="3">
         <v>1002900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>971500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1050300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1081900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>922500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>891100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>659200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>628600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>594300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>574600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>563500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>506300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>503300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>474200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>469400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>452700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>455100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>416300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>423600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>428400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>346100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>335900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>348300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>375000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>373000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>449400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>446100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>436500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>442200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5500,8 +5649,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5595,8 +5747,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5690,103 +5845,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6349600</v>
+      </c>
+      <c r="E66" s="3">
         <v>6455700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6429600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6605000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6828600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5393300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5228600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>4533200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>3190300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2852800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2720200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2714700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2624800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2721400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2607100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2693800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2834200</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2779400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2636400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2693700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2704500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2616300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2550800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5820,8 +5981,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5915,8 +6077,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6010,8 +6175,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6105,8 +6273,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6200,103 +6371,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3814400</v>
+      </c>
+      <c r="E72" s="3">
         <v>3733300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3648700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3523700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3271300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3085500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2929000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2737900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2535900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2347800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2192100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2045300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1848700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1696900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1652200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1551100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1485600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1400100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1157500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1131800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1105500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1087500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1046900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>981200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>875500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>867700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>858600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>852800</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6390,8 +6567,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6485,8 +6665,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6580,103 +6763,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4593100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4605400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4380700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4368200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4032500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>3809000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3580100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3493500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3425300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3281000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3205500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3118600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2966600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2891900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2773900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2633400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2543600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2565800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2308500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2342900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2290500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2273000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2254400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6770,203 +6959,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45290</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44562</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44198</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43827</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43463</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43099</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E81" s="3">
         <v>84500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>125000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>252400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>185800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>156600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>191100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>202000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>188100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>155800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>146800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>196600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>151800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>44700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>101100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>65400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>85500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>242600</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>25700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>26300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>18000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>40600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-6000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>97300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>105700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>40500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7000,103 +7198,107 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>127500</v>
+      </c>
+      <c r="E83" s="3">
         <v>137900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>126000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>122100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>116000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>117400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>105000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>93100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>79200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>80800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>77800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>78500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>96500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>85700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>83300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>84700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>86500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>80400</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>79500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>79200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>85300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>78800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>78500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>78600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>80800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>77200</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>73000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>71100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>77500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7190,8 +7392,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7285,8 +7490,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7380,8 +7588,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7475,8 +7686,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7570,103 +7784,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>263900</v>
+      </c>
+      <c r="E89" s="3">
         <v>217000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>276600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>217300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>188400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>175300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>277400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>208800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>152200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>252400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>154100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>159100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>138800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>154200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>206800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>229100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>34500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>99900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>108400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>105700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>48600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>198900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>71700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>101100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>26900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>141800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>71200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>103100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>94500</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>110500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7700,103 +7920,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-93800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-174900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-146200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-123000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-111300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-134200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-105600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-79900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-71600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-82400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-65600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-65300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-60800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-95200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-61600</v>
       </c>
       <c r="S91" s="3">
         <v>-61600</v>
       </c>
       <c r="T91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="U91" s="3">
         <v>-114400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-77200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-83600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-84300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-108200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-74600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7890,8 +8114,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7985,103 +8212,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-291000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-168800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-158300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-193800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-598000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-294500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-270500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-89800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-65600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-64300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-123300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-61500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-64600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-103200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-72100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-83000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-79800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-153600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-78200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8115,8 +8348,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8210,8 +8444,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8305,8 +8542,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8400,8 +8640,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8495,289 +8738,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>48800</v>
+      </c>
+      <c r="E100" s="3">
         <v>-25900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-117900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-152700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1172800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>325300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1176700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>180900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>18700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-69200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-89800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-81000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-19500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-159500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-168400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>40400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>5300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-49200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-32100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>21200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-17600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-21300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>46200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>25600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>2900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-6900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-4900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>5100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>3900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>10900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>28200</v>
+      </c>
+      <c r="E102" s="3">
         <v>10900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>111700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>47300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>30500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-10600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>6500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>15800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-17800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-8700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-11500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>25800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-22700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>16100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>24300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,438 +656,451 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45290</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44562</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44198</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43827</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43463</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43099</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1455300</v>
+      </c>
+      <c r="E8" s="3">
         <v>1420300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1614100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1625200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1757600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1791200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1768100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1747600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1650200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1366300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1310100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1185900</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1198700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1046700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1019800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>850600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>848700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>852800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>859400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>842000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>827300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>835100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>853100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>812600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>846600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>875400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>952500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>936300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>894900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>878500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>881100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1128400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1116700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1177700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1238700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1359700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1367000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1379300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1371200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1231500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1020600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>988900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>859600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>878100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>772800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>768600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>637500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>633800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>649600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>640100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>656000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>643000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>648000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>667600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>649200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>654100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>678200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>688400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>326900</v>
+      </c>
+      <c r="E10" s="3">
         <v>303600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>436400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>386500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>397900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>424200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>388800</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>376400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>418700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>345700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>321200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>326300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>320600</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>273900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>251200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>213100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>214900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>203200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>219300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>186000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>184300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>187100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>185500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>163400</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>192500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>197200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>192700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1135,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1234,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,92 +1335,95 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>14900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>3400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>2600</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>23800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>4500</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>13900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>3800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1400</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
         <v>0</v>
       </c>
       <c r="P14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="3">
         <v>800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>38200</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
+      <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-3000</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>12100</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>54000</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>900</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
         <v>0</v>
       </c>
@@ -1416,106 +1436,112 @@
       <c r="AH14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E15" s="3">
         <v>127500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>137900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>126000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>122100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>116000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>117400</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>105000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>93100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>79200</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>80800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>77800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>79200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>78500</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>96500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>85700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>83300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>84700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>86500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>80400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>79500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>79200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>85300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>78800</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>78500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>78600</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>80800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>77200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>73000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>71100</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>77500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1547,204 +1573,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1306800</v>
+      </c>
+      <c r="E17" s="3">
         <v>1283100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1455300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1446800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1400900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1535300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1518900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1479300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1371600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1133400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1099000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>980300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>930400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>847200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>945500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>723100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>742400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>730000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>563200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>782200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>765300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>810800</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>779400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>794000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>864000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>843600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>917300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>901900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>856800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>846000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>845700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>148500</v>
+      </c>
+      <c r="E18" s="3">
         <v>137200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>158800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>178400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>356700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>255900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>249200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>268300</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>278600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>232900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>211100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>205600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>268300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>199500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>74300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>127500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>106300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>122800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>296200</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>59800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>62000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>24300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>73700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>18600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>31800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>35200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>34400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>38100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>32500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>35400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1779,498 +1812,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E20" s="3">
         <v>11200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>4100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>4600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>9400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>11300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-5900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>600</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>1400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2800</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>20500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>13000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>93100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>9000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2400</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>34900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>276000</v>
+      </c>
+      <c r="E21" s="3">
         <v>275900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>300900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>309000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>488200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>383100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>360700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>372300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>369300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>311700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>291200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>284100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>347500</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>277100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>169700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>210900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>187700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>208200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>384100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>137500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>139200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>124000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>155700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>92400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>74000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>203500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>125000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>114700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>113500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>102000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>147800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>69200</v>
+      </c>
+      <c r="E22" s="3">
         <v>62900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>68500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>70300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>50300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>46100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>39800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>24000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>15600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>16400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>18800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>17900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>19100</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18600</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>20900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20200</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>23000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>22300</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22500</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>21700</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>82100</v>
+      </c>
+      <c r="E23" s="3">
         <v>85500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>94500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>112700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>295900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>216800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>197200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>227500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>252200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>216800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>195400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>190800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>253000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>182100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>56400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>106400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>86400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>104400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>279000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>37700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>38800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>24900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>50200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>101800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>21900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>15000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>18100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>47900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>800</v>
+      </c>
+      <c r="E24" s="3">
         <v>3900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>7200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-15400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40700</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>38000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>35200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>47300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>37800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>42600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>55000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>28700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>10200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>19900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>18300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>35600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>10900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>7800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>5300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>9700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>6300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>7700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2367,204 +2416,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>81400</v>
+      </c>
+      <c r="E26" s="3">
         <v>81600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>87300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>128100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>255200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>189900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>159200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>192300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>204800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>190700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>157600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>148200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>198100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>153400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>46100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>101600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>66500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>86100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>243400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>26800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>31000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>19600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>40400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>98100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>70200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>8700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>10300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>41700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E27" s="3">
         <v>81200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>84500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>125000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>252400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>185800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>156600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>191100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>202000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>188100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>155800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>146800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>196600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>151800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>44700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>101100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>65400</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>85500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>242600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>25700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>26300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>18000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>38900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>97300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>69000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>40500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2661,8 +2719,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2711,8 +2772,8 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2729,11 +2790,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1700</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2741,11 +2802,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2759,8 +2820,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2857,8 +2921,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2955,204 +3022,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-2900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-11200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-4100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-4600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-9400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-11300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>5900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-600</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-1400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2800</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-20500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>3300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E33" s="3">
         <v>81200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>84500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>125000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>252400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>185800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>156600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>191100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>202000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>188100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>155800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>146800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>196600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>151800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>44700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>101100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>65400</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>85500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>242600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>25700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>26300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>18000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>40600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>97300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>105700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>40500</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3249,209 +3325,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E35" s="3">
         <v>81200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>84500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>125000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>252400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>185800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>156600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>191100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>202000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>188100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>155800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>146800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>196600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>151800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>44700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>101100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>65400</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>85500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>242600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>25700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>26300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>18000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>40600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>97300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>105700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>40500</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45290</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44562</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44198</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43827</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43463</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43099</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3486,8 +3571,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3522,106 +3608,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>121600</v>
+      </c>
+      <c r="E41" s="3">
         <v>145500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>126500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>119000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>111500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>132600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>127000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>126000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>146700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>99500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>68900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>67200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>77700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>71200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>81600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>65800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>76200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>72900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>69100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>87000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>95700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>107300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>81500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>104100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>122900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>106800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>110100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>124800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>138900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>114600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3718,694 +3808,718 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>611300</v>
+      </c>
+      <c r="E43" s="3">
         <v>656400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>821900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>761300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>769300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>770900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>695200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>687300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>602100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>542800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>470200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>482600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>436100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>388900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>409300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>377500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>379700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>400800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>409700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>360000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>363200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>375400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>392200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>371700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>378300</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>418400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>396400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>420300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>389300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>396800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>395900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>627700</v>
+      </c>
+      <c r="E44" s="3">
         <v>687500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>758700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>822800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>825100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>828800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>673600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>642000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>578400</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>491700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>457500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>476300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>428200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>420700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>405900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>406800</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>394700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>381400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>363000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>353000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>348300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>339900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>341000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>361700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>370600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>373100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>358200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>375100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>359600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>342100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>330800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>146900</v>
+      </c>
+      <c r="E45" s="3">
         <v>130000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>148500</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>140000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>170000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>170300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>142300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>106700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>134600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>125000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>92500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>77500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>80600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>60000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>90200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>81000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>80500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>71500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>71700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>68600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>60100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>57500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>63700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>65300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>56700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>95100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>56700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>51100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>49500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>52000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1507500</v>
+      </c>
+      <c r="E46" s="3">
         <v>1619300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1855700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1843000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1876000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1902500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1638100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1562000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1461800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1259000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1089000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1103600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1022600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>940800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>987000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>931200</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>931100</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>930100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>917300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>853700</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>867100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>871200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>897900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>878500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>918200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>971100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>956400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>962200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>924900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>927300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>893300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2415500</v>
+      </c>
+      <c r="E47" s="3">
         <v>2378500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2251600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2164200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2214300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2125100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1926400</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1814600</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1736200</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1563800</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1349200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1107800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1037400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>915100</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>804700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>742900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>729100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>802200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>689400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>447700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>458000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>433400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>410200</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>398800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>399100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>409100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>302000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>290000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>279800</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>270900</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>292700</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3050800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3126200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3140700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3001700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2971100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2901800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2648200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2520800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2414500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2033000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1995500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1995300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2011800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1967300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2010400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1931400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1908200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1888000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1927100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1833800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1843200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1821300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1687900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3410800</v>
+      </c>
+      <c r="E49" s="3">
         <v>3555600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3560400</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3538800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3640800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3678700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2835500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2773900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2315900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1646200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1616900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1649600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1684600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1693800</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1733900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1714100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1702300</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="U49" s="3">
-        <v>1749700</v>
       </c>
       <c r="V49" s="3">
         <v>1749700</v>
       </c>
       <c r="W49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="X49" s="3">
         <v>1799500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1801700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1825000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4502,8 +4616,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4600,106 +4717,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>236000</v>
+      </c>
+      <c r="E52" s="3">
         <v>263100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>252700</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>262700</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>271100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>252900</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>154200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>137500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>98200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>113600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>83000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>69300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>76900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>74500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>77400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>61400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>56500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>57200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>61800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>60000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>68700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>67500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>68400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>70100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>71400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>78200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>76300</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>64200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>65300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>57800</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>58600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4796,106 +4919,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10620600</v>
+      </c>
+      <c r="E54" s="3">
         <v>10942800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>11061100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10810300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10973200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10861100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>9202400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>8808800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8026700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6615600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6133700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>5925700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5833300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5591400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5613300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5381000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5327200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5377800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5345300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>4944900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5036600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4995100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4889400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4930,8 +5059,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4966,596 +5096,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>349500</v>
+      </c>
+      <c r="E57" s="3">
         <v>343400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>425600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>394700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>427100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>433800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>472500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>398200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>414600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>351300</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>307100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>272800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>264400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>245600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>255300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>207000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>197500</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>211600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>239300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>192000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>208900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>192500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>219500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>177800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>185200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>188000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>217400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>213600</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>186500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>181400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>180900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E58" s="3">
         <v>103100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>60700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>73900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>88100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>118800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>69800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>63700</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>32700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>35300</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>24400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>55100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>41600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>27000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>26200</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>42800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>86400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>91000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>61100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>35900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>23700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>7500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>11100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>16700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>18200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>19400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>25000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>23200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>521300</v>
+      </c>
+      <c r="E59" s="3">
         <v>520800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>511800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>565100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>498400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>546400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>526100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>566100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>472500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>426800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>421200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>428200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>386200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>365100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>392400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>390400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>366000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>353800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>358100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>342800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>321500</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>330000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>313500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>297000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>290100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>302100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>325900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>314500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>283200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>245400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>247700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>963100</v>
+      </c>
+      <c r="E60" s="3">
         <v>967300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>998100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1033700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1013500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1099000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1068400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1028000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>919800</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>813400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>752700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>756200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>692200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>637700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>675300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>623600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>606300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>651700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>688300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>595900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>566300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>546200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>540500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>485800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>482700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>506900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>559500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>546300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>489000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>451800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>451900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4317100</v>
+      </c>
+      <c r="E61" s="3">
         <v>4362900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4366400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4338100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4458800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4558600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3315000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3220900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2881100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1677900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1439000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1325700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1393800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1417500</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1480500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1448000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1553100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1664900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1558400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1559800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1640100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1663800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1666900</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>797900</v>
+      </c>
+      <c r="E62" s="3">
         <v>929600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1002900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>971500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1050300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1081900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>922500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>891100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>659200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>628600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>594300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>574600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>563500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>506300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>503300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>474200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>469400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>452700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>455100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>416300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>423600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>428400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>346100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>335900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>348300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>375000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>373000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>449400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>446100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>436500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>442200</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5652,8 +5801,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5750,8 +5902,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5848,106 +6003,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>6159700</v>
+      </c>
+      <c r="E66" s="3">
         <v>6349600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6455700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6429600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6605000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6828600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5393300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5228600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>4533200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3190300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2852800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2720200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2714700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2624800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2721400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2607100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2693800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2834200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2779400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2636400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2693700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2704500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2616300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5982,8 +6143,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6080,8 +6242,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6178,8 +6343,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6276,8 +6444,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6374,106 +6545,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3893300</v>
+      </c>
+      <c r="E72" s="3">
         <v>3814400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3733300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3648700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3523700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3271300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3085500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2929000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2737900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2535900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2347800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2192100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2045300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1848700</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1696900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1652200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1551100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1485600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1400100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1157500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1131800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1105500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1087500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>981200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>875500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>867700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>858600</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>852800</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6570,8 +6747,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6668,8 +6848,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6766,106 +6949,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4460900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4593100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4605400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4380700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4368200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4032500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>3809000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3580100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3493500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3425300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3281000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3205500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3118600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2966600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2891900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2773900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2633400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2543600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2565800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2308500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2342900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2290500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2273000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6962,209 +7151,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45290</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44562</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44198</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43827</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43463</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43099</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>78900</v>
+      </c>
+      <c r="E81" s="3">
         <v>81200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>84500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>125000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>252400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>185800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>156600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>191100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>202000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>188100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>155800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>146800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>196600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>151800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>44700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>101100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>65400</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>85500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>242600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>25700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>26300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>18000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>40600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>97300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>105700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>40500</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7199,106 +7397,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>124600</v>
+      </c>
+      <c r="E83" s="3">
         <v>127500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>137900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>126000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>122100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>116000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>117400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>105000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>93100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>80800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>77800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>78500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>96500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>85700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>83300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>84700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>86500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>80400</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>79500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>79200</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>85300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>78800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>78500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>78600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>80800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>77200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>73000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>71100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>77500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7395,8 +7597,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7493,8 +7698,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7591,8 +7799,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7689,8 +7900,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7787,106 +8001,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E89" s="3">
         <v>263900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>217000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>276600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>217300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>188400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>175300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>277400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>208800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>152200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>252400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>154100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>159100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>138800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>154200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>206800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>229100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>34500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>99900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>108400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>105700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>48600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>198900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>71700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>101100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>26900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>141800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>71200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>103100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>94500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>110500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7921,106 +8141,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-93800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-174900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-146200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-123000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-111300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-134200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-105600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-79900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-71600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-82400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-65600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-60800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-95200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="S91" s="3">
-        <v>-61600</v>
       </c>
       <c r="T91" s="3">
         <v>-61600</v>
       </c>
       <c r="U91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="V91" s="3">
         <v>-114400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-77200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-83600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-84300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-108200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8117,8 +8341,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8215,106 +8442,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-291000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-168800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-158300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-91600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-193800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-598000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-294500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-270500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-89800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-65600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-64300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-123300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-61500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-61200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-64600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-103200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-72100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-83000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-79800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-153600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8349,8 +8582,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8447,8 +8681,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8545,8 +8782,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8643,8 +8883,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8741,298 +8984,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-81000</v>
+      </c>
+      <c r="E100" s="3">
         <v>48800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-25900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-117900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-152700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1172800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>325300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1176700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>180900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>18700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-69200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-89800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-81000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-19500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-159500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-168400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>40400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>5300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-49200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-32100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>21200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-17600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>46200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>6500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>1200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-5600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>2900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>4400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-6900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>1700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-4900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>5100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>10900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>300</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E102" s="3">
         <v>28200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>10900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>111700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2800</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>47300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>30500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-10600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>6500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>15800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-17800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-8700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>25800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>16100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>24300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,451 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45290</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44562</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44198</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43827</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43463</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43099</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1421900</v>
+      </c>
+      <c r="E8" s="3">
         <v>1455300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1420300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1614100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1625200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1757600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1791200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1768100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1747600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1650200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1366300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1310100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1185900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1198700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1046700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1019800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>850600</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>848700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>852800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>859400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>842000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>827300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>835100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>853100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>812600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>846600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>875400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>952500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>936300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>894900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>878500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>881100</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1108300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1128400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1116700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1177700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1238700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1359700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1367000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1379300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1371200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1231500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1020600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>988900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>859600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>878100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>772800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>768600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>637500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>633800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>649600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>640100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>656000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>643000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>648000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>667600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>649200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>654100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>678200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>688400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>313600</v>
+      </c>
+      <c r="E10" s="3">
         <v>326900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>303600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>436400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>386500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>397900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>424200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>388800</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>376400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>418700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>345700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>321200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>326300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>320600</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>273900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>251200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>213100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>214900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>203200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>219300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>186000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>184300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>187100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>185500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>163400</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>192500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>197200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>192700</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,8 +1149,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1237,8 +1251,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,95 +1355,98 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1100</v>
+        <v>16600</v>
       </c>
       <c r="E14" s="3">
-        <v>4100</v>
+        <v>-31800</v>
       </c>
       <c r="F14" s="3">
-        <v>14900</v>
+        <v>-21800</v>
       </c>
       <c r="G14" s="3">
-        <v>3400</v>
+        <v>11700</v>
       </c>
       <c r="H14" s="3">
-        <v>2600</v>
+        <v>-1200</v>
       </c>
       <c r="I14" s="3">
-        <v>11500</v>
+        <v>-4600</v>
       </c>
       <c r="J14" s="3">
+        <v>11200</v>
+      </c>
+      <c r="K14" s="3">
         <v>23800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>4500</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>13900</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>3800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1400</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
       <c r="P14" s="3">
         <v>0</v>
       </c>
       <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
         <v>800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>38200</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3000</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
       <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>12100</v>
       </c>
-      <c r="Y14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>54000</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>900</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
         <v>0</v>
       </c>
@@ -1439,109 +1459,115 @@
       <c r="AI14" s="3">
         <v>0</v>
       </c>
+      <c r="AJ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123600</v>
+      </c>
+      <c r="E15" s="3">
         <v>124600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>127500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>137900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>126000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>122100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>116000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>117400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>105000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>93100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>79200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>80800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>77800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>79200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>78500</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>96500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>85700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>83300</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>84700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>86500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>80400</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>79500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>79200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>85300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>78800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>78500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>78600</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>80800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>77200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>73000</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>71100</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>77500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1574,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>1306800</v>
+        <v>1348000</v>
       </c>
       <c r="E17" s="3">
-        <v>1283100</v>
+        <v>1383200</v>
       </c>
       <c r="F17" s="3">
-        <v>1455300</v>
+        <v>1383800</v>
       </c>
       <c r="G17" s="3">
-        <v>1446800</v>
+        <v>1448000</v>
       </c>
       <c r="H17" s="3">
-        <v>1400900</v>
+        <v>1503000</v>
       </c>
       <c r="I17" s="3">
-        <v>1535300</v>
+        <v>1619100</v>
       </c>
       <c r="J17" s="3">
+        <v>1619000</v>
+      </c>
+      <c r="K17" s="3">
         <v>1518900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1479300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1371600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1133400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1099000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>980300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>930400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>847200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>945500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>723100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>742400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>730000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>563200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>782200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>765300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>810800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>779400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>794000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>864000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>843600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>917300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>901900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>856800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>846000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>845700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>148500</v>
+        <v>73900</v>
       </c>
       <c r="E18" s="3">
-        <v>137200</v>
+        <v>72100</v>
       </c>
       <c r="F18" s="3">
-        <v>158800</v>
+        <v>36500</v>
       </c>
       <c r="G18" s="3">
-        <v>178400</v>
+        <v>166100</v>
       </c>
       <c r="H18" s="3">
-        <v>356700</v>
+        <v>122200</v>
       </c>
       <c r="I18" s="3">
-        <v>255900</v>
+        <v>138500</v>
       </c>
       <c r="J18" s="3">
+        <v>172100</v>
+      </c>
+      <c r="K18" s="3">
         <v>249200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>268300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>278600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>232900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>211100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>205600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>268300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>199500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>74300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>127500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>106300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>122800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>296200</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>59800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>62000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>24300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>73700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>18600</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>31800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>35200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>34400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>38100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>32500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>35400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1813,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>2900</v>
+        <v>-11300</v>
       </c>
       <c r="E20" s="3">
-        <v>11200</v>
+        <v>-47500</v>
       </c>
       <c r="F20" s="3">
-        <v>4100</v>
+        <v>-90100</v>
       </c>
       <c r="G20" s="3">
-        <v>4600</v>
+        <v>-8600</v>
       </c>
       <c r="H20" s="3">
-        <v>9400</v>
+        <v>-59600</v>
       </c>
       <c r="I20" s="3">
-        <v>11300</v>
+        <v>-223000</v>
       </c>
       <c r="J20" s="3">
+        <v>-106200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-5900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>600</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>-900</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>1400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2800</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>20500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>13000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>93100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>9000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2400</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>34900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>276000</v>
+        <v>208700</v>
       </c>
       <c r="E21" s="3">
-        <v>275900</v>
+        <v>244200</v>
       </c>
       <c r="F21" s="3">
-        <v>300900</v>
+        <v>254100</v>
       </c>
       <c r="G21" s="3">
-        <v>309000</v>
+        <v>312600</v>
       </c>
       <c r="H21" s="3">
-        <v>488200</v>
+        <v>307800</v>
       </c>
       <c r="I21" s="3">
-        <v>383100</v>
+        <v>483600</v>
       </c>
       <c r="J21" s="3">
+        <v>394400</v>
+      </c>
+      <c r="K21" s="3">
         <v>360700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>372300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>369300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>311700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>291200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>284100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>347500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>277100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>169700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>210900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>187700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>208200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>384100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>137500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>139200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>124000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>155700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>92400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>74000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>203500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>125000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>114700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>113500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>102000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>147800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>66800</v>
+      </c>
+      <c r="E22" s="3">
         <v>69200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>62900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>68500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>70300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>70200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>50300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>39800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>24000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>15600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>16400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>18800</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>17900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>19100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18600</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>20900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20200</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>23000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22300</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>21700</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>22400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E23" s="3">
         <v>82100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>85500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>94500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>112700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>295900</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>216800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>197200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>227500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>252200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>216800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>195400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>190800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>253000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>182100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>56400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>106400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>86400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>104400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>279000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>37700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>38800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>24900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>50200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>101800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>21900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>15000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>18100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9200</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>47900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-17500</v>
+      </c>
+      <c r="E24" s="3">
         <v>800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>7200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-15400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>40700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>27000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>38000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>35200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>47300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>37800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>42600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>55000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>28700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>10200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>19900</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>18300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>35600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>7800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>5300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>9700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>6300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>7700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2419,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>19100</v>
+      </c>
+      <c r="E26" s="3">
         <v>81400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>81600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>87300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>128100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>255200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>189900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>159200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>192300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>204800</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>190700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>157600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>148200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>198100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>153400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>46100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>101600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>66500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>86100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>243400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>26800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>31000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>19600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>40400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>98100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>70200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>8700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>10300</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>41700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E27" s="3">
         <v>78900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>81200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>84500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>125000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>252400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>185800</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>156600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>191100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>202000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>188100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>155800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>146800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>196600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>151800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>44700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>101100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>65400</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>85500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>242600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>25700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>26300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>18000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>38900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>97300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>69000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>7800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>9100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>40500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2722,8 +2780,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2775,8 +2836,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2793,11 +2854,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2805,11 +2866,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2823,8 +2884,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2924,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3025,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-2900</v>
+        <v>11300</v>
       </c>
       <c r="E32" s="3">
-        <v>-11200</v>
+        <v>47500</v>
       </c>
       <c r="F32" s="3">
-        <v>-4100</v>
+        <v>90100</v>
       </c>
       <c r="G32" s="3">
-        <v>-4600</v>
+        <v>8600</v>
       </c>
       <c r="H32" s="3">
-        <v>-9400</v>
+        <v>59600</v>
       </c>
       <c r="I32" s="3">
-        <v>-11300</v>
+        <v>223000</v>
       </c>
       <c r="J32" s="3">
+        <v>106200</v>
+      </c>
+      <c r="K32" s="3">
         <v>5900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-600</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>900</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-1400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2800</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-20500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>3300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1600</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E33" s="3">
         <v>78900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>81200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>84500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>125000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>252400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>185800</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>156600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>191100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>202000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>188100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>155800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>146800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>196600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>151800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>44700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>101100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>65400</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>85500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>242600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>25700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>26300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>18000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>97300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>105700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>7800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>9100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>40500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3328,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E35" s="3">
         <v>78900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>81200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>84500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>125000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>252400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>185800</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>156600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>191100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>202000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>188100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>155800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>146800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>196600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>151800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>44700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>101100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>65400</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>85500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>242600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>25700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>26300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>18000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>97300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>105700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>7800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>9100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>40500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45290</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44562</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44198</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43827</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43463</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43099</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3572,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3609,109 +3695,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>114800</v>
+      </c>
+      <c r="E41" s="3">
         <v>121600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>145500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>126500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>119000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>111500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>132600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>127000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>126000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>146700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>99500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>68900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>67200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>77700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>71200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>81600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>65800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>76200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>76300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>72900</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>69100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>87000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>95700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>107300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>81500</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>104100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>122900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>106800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>110100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>124800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>138900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>114600</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3811,715 +3901,739 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>616700</v>
+      </c>
+      <c r="E43" s="3">
         <v>611300</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>656400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>821900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>761300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>769300</v>
       </c>
-      <c r="I43" s="3">
-        <v>770900</v>
-      </c>
       <c r="J43" s="3">
+        <v>795900</v>
+      </c>
+      <c r="K43" s="3">
         <v>695200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>687300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>602100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>542800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>470200</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>482600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>436100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>388900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>409300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>377500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>379700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>400800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>409700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>360000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>363200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>375400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>392200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>371700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>378300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>418400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>396400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>420300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>389300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>396800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>395900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>617800</v>
+      </c>
+      <c r="E44" s="3">
         <v>627700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>687500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>758700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>822800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>825100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>828800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>673600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>642000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>578400</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>491700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>457500</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>476300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>428200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>420700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>405900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>406800</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>394700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>381400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>363000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>353000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>348300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>339900</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>341000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>361700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>370600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>373100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>358200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>375100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>359600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>342100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>330800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>146900</v>
+        <v>23600</v>
       </c>
       <c r="E45" s="3">
-        <v>130000</v>
+        <v>31900</v>
       </c>
       <c r="F45" s="3">
-        <v>148500</v>
+        <v>28200</v>
       </c>
       <c r="G45" s="3">
-        <v>140000</v>
+        <v>42600</v>
       </c>
       <c r="H45" s="3">
-        <v>170000</v>
+        <v>38100</v>
       </c>
       <c r="I45" s="3">
-        <v>170300</v>
+        <v>53200</v>
       </c>
       <c r="J45" s="3">
+        <v>36200</v>
+      </c>
+      <c r="K45" s="3">
         <v>142300</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>106700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>134600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>125000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>92500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>77500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>80600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>60000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>90200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>81000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>80500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>71500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>71600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>68600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>60100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>57500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>63700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>65300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>56700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>95100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>56700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>51100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>49500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>52000</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1496900</v>
+      </c>
+      <c r="E46" s="3">
         <v>1507500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1619300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1855700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1843000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1876000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1902500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1638100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1562000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1461800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1259000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1089000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1103600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1022600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>940800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>987000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>931200</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>931100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>930100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>917300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>853700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>867100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>871200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>897900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>878500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>918200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>971100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>956400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>962200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>924900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>927300</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>893300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2332000</v>
+      </c>
+      <c r="E47" s="3">
         <v>2415500</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2378500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2251600</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2164200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2214300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2125100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1926400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1814600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1736200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1563800</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1349200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1107800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1037400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>915100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>804700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>742900</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>729100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>802200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>689400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>447700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>458000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>433400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>410200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>398800</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>399100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>409100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>302000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>290000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>279800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>270900</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>292700</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3069700</v>
+      </c>
+      <c r="E48" s="3">
         <v>3050800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3126200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3140700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3001700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2971100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2901800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2648200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2520800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2414500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2033000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1995500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1995300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2011800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1967300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2010400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1931400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1908200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1888000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1927100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1833800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1843200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1821300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3433300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3410800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3555600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3560400</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3538800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3640800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3678700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2835500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2773900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2315900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1646200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1616900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1649600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1684600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1693800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1733900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1714100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1702300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="V49" s="3">
-        <v>1749700</v>
       </c>
       <c r="W49" s="3">
         <v>1749700</v>
       </c>
       <c r="X49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="Y49" s="3">
         <v>1799500</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1801700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4619,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4720,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>236000</v>
+        <v>222100</v>
       </c>
       <c r="E52" s="3">
-        <v>263100</v>
+        <v>218800</v>
       </c>
       <c r="F52" s="3">
-        <v>252700</v>
+        <v>246600</v>
       </c>
       <c r="G52" s="3">
-        <v>262700</v>
+        <v>235000</v>
       </c>
       <c r="H52" s="3">
-        <v>271100</v>
+        <v>238100</v>
       </c>
       <c r="I52" s="3">
-        <v>252900</v>
+        <v>246000</v>
       </c>
       <c r="J52" s="3">
+        <v>232000</v>
+      </c>
+      <c r="K52" s="3">
         <v>154200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>137500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>98200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>113600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>83000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>69300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>76900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>74500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>77400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>61400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>56500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>57200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>60000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>68700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>67500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>68400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>70100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>71400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>78200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>76300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>64200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>65300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>57800</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>58600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4922,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10572700</v>
+      </c>
+      <c r="E54" s="3">
         <v>10620600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10942800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>11061100</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10810300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10973200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10861100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>9202400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>8808800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8026700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6615600</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6133700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>5925700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5833300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5591400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5613300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5381000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5327200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5377800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5345300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>4944900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5036600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4995100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5060,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5097,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>331700</v>
+      </c>
+      <c r="E57" s="3">
         <v>349500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>343400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>425600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>394700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>427100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>433800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>472500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>398200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>414600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>351300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>307100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>272800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>264400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>245600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>255300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>207000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>197500</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>211600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>239300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>192000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>208900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>192500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>219500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>177800</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>185200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>188000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>217400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>213600</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>186500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>181400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>180900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>92300</v>
+        <v>174000</v>
       </c>
       <c r="E58" s="3">
-        <v>103100</v>
+        <v>150100</v>
       </c>
       <c r="F58" s="3">
-        <v>60700</v>
+        <v>162600</v>
       </c>
       <c r="G58" s="3">
-        <v>73900</v>
+        <v>116000</v>
       </c>
       <c r="H58" s="3">
-        <v>88100</v>
+        <v>126200</v>
       </c>
       <c r="I58" s="3">
-        <v>118800</v>
+        <v>136500</v>
       </c>
       <c r="J58" s="3">
+        <v>164200</v>
+      </c>
+      <c r="K58" s="3">
         <v>69800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>63700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>32700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>35300</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>24400</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>55100</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>41600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>27000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>26200</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>42800</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>86400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>91000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>61100</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>35900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>23700</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>7500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>11100</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>16700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>18200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>19400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>25000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>23200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>521300</v>
+        <v>92300</v>
       </c>
       <c r="E59" s="3">
-        <v>520800</v>
+        <v>13300</v>
       </c>
       <c r="F59" s="3">
-        <v>511800</v>
+        <v>11700</v>
       </c>
       <c r="G59" s="3">
-        <v>565100</v>
+        <v>15500</v>
       </c>
       <c r="H59" s="3">
-        <v>498400</v>
+        <v>18300</v>
       </c>
       <c r="I59" s="3">
-        <v>546400</v>
+        <v>29800</v>
       </c>
       <c r="J59" s="3">
+        <v>38400</v>
+      </c>
+      <c r="K59" s="3">
         <v>526100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>566100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>472500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>426800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>421200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>428200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>386200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>365100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>392400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>390400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>366000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>353800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>358100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>342800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>321500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>330000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>313500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>297000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>290100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>302100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>325900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>314500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>283200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>245400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>247700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1062500</v>
+      </c>
+      <c r="E60" s="3">
         <v>963100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>967300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>998100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1033700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1013500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1099000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1068400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1028000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>919800</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>813400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>752700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>756200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>692200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>637700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>675300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>623600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>606300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>651700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>688300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>595900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>566300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>546200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>540500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>485800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>482700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>506900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>559500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>546300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>489000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>451800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>451900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4317100</v>
+        <v>4290300</v>
       </c>
       <c r="E61" s="3">
-        <v>4362900</v>
+        <v>4473600</v>
       </c>
       <c r="F61" s="3">
-        <v>4366400</v>
+        <v>4524200</v>
       </c>
       <c r="G61" s="3">
-        <v>4338100</v>
+        <v>4521300</v>
       </c>
       <c r="H61" s="3">
-        <v>4458800</v>
+        <v>4493000</v>
       </c>
       <c r="I61" s="3">
-        <v>4558600</v>
+        <v>4608000</v>
       </c>
       <c r="J61" s="3">
+        <v>4703200</v>
+      </c>
+      <c r="K61" s="3">
         <v>3315000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3220900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2881100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1677900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1439000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1325700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1393800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1417500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1480500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1448000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1553100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1664900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1558400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1559800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1640100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1663800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>797900</v>
+        <v>189600</v>
       </c>
       <c r="E62" s="3">
-        <v>929600</v>
+        <v>219900</v>
       </c>
       <c r="F62" s="3">
-        <v>1002900</v>
+        <v>283400</v>
       </c>
       <c r="G62" s="3">
-        <v>971500</v>
+        <v>329100</v>
       </c>
       <c r="H62" s="3">
-        <v>1050300</v>
+        <v>291800</v>
       </c>
       <c r="I62" s="3">
-        <v>1081900</v>
+        <v>316600</v>
       </c>
       <c r="J62" s="3">
+        <v>391900</v>
+      </c>
+      <c r="K62" s="3">
         <v>922500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>891100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>659200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>628600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>594300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>574600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>563500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>506300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>503300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>474200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>469400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>452700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>455100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>416300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>423600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>428400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>346100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>335900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>348300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>375000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>373000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>449400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>446100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>436500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>442200</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5804,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5905,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6006,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>6159700</v>
+        <v>5938400</v>
       </c>
       <c r="E66" s="3">
-        <v>6349600</v>
+        <v>6078000</v>
       </c>
       <c r="F66" s="3">
-        <v>6455700</v>
+        <v>6259800</v>
       </c>
       <c r="G66" s="3">
-        <v>6429600</v>
+        <v>6367400</v>
       </c>
       <c r="H66" s="3">
-        <v>6605000</v>
+        <v>6343400</v>
       </c>
       <c r="I66" s="3">
-        <v>6828600</v>
+        <v>6522700</v>
       </c>
       <c r="J66" s="3">
+        <v>6739500</v>
+      </c>
+      <c r="K66" s="3">
         <v>5393300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5228600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>4533200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3190300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2852800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2720200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2714700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2624800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2721400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2607100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2693800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2834200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2779400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2636400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2693700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2704500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6144,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6245,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6346,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6447,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6548,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3910200</v>
+      </c>
+      <c r="E72" s="3">
         <v>3893300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3814400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3733300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3648700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3523700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3271300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3085500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2929000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2737900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2535900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2347800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2192100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2045300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1848700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1696900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1652200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1551100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1485600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1400100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1157500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1131800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1105500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>981200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>875500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>867700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>858600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>852800</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6750,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6851,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6952,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4551400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4460900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4593100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4605400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4380700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4368200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4032500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>3809000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3580100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3493500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3425300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3281000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3205500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3118600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2966600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2891900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2773900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2633400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2543600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2565800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2308500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2342900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2290500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7154,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45290</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44562</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44198</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43827</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43463</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43099</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16900</v>
+      </c>
+      <c r="E81" s="3">
         <v>78900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>81200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>84500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>125000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>252400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>185800</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>156600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>191100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>202000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>188100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>155800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>146800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>196600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>151800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>44700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>101100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>65400</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>85500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>242600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>25700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>26300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>18000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>97300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>105700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>7800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>9100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>40500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7398,109 +7596,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>124600</v>
+        <v>93800</v>
       </c>
       <c r="E83" s="3">
-        <v>127500</v>
+        <v>88700</v>
       </c>
       <c r="F83" s="3">
-        <v>137900</v>
+        <v>89900</v>
       </c>
       <c r="G83" s="3">
-        <v>126000</v>
+        <v>91500</v>
       </c>
       <c r="H83" s="3">
-        <v>122100</v>
+        <v>79700</v>
       </c>
       <c r="I83" s="3">
-        <v>116000</v>
+        <v>72100</v>
       </c>
       <c r="J83" s="3">
+        <v>62700</v>
+      </c>
+      <c r="K83" s="3">
         <v>117400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>105000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>93100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>80800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>77800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>79200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>78500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>96500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>85700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>83300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>84700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>86500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>80400</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>79500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>79200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>85300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>78800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>78500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>78600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>80800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>77200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>73000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>71100</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>77500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7600,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7701,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7802,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7903,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8004,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>274500</v>
+      </c>
+      <c r="E89" s="3">
         <v>146500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>263900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>217000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>276600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>217300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>188400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>175300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>277400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>208800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>152200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>252400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>154100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>159100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>138800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>154200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>206800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>229100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>34500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>99900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>108400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>105700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>48600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>198900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>71700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>101100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>26900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>141800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>71200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>103100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>94500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>110500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8142,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-67400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-98000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-93800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-174900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-146200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-123000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-111300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-134200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-105600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-79900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-71600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-82400</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-60800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-95200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="T91" s="3">
-        <v>-61600</v>
       </c>
       <c r="U91" s="3">
         <v>-61600</v>
       </c>
       <c r="V91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="W91" s="3">
         <v>-114400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-77200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-83600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-84300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8344,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8445,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-64900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-96700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-291000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-168800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-158300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-91600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-193800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-598000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-294500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-270500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-89800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-64300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-123300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-61500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-61200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-64600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-103200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-72100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-83000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-79800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8583,31 +8816,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8684,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8785,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8886,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8987,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-201000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-81000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>48800</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-25900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-117900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-152700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1172800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-4300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>325300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1176700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>180900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>18700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-69200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-89800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-81000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-19500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-159500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-168400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>40400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>5300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-49200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-32100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>21200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>46200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>4100</v>
+        <v>9000</v>
       </c>
       <c r="E101" s="3">
-        <v>6500</v>
+        <v>9300</v>
       </c>
       <c r="F101" s="3">
-        <v>-11400</v>
+        <v>7300</v>
       </c>
       <c r="G101" s="3">
-        <v>9000</v>
+        <v>25600</v>
       </c>
       <c r="H101" s="3">
-        <v>9300</v>
+        <v>-4200</v>
       </c>
       <c r="I101" s="3">
-        <v>7300</v>
+        <v>-7900</v>
       </c>
       <c r="J101" s="3">
+        <v>-8100</v>
+      </c>
+      <c r="K101" s="3">
         <v>25600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7900</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>1200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>2900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>4400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>3900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-6900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-4900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>5100</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>3900</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>5400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>10900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>300</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-27000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>28200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>10900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>9400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>111700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>47300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>30500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-10600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>6500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>15800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-17800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-11500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>25800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>16100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>24300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,464 +656,476 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="19" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45290</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44562</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44198</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43827</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43463</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43099</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1417700</v>
+      </c>
+      <c r="E8" s="3">
         <v>1421900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1455300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1420300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1614100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1625200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1757600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1791200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1768100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1747600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1650200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1366300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1310100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1185900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1198700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1046700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1019800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>850600</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>848700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>852800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>859400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>842000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>827300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>835100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>853100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>812600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>846600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>875400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>952500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>936300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>894900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>878500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>881100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1083900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1108300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1128400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1116700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1177700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1238700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1359700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1367000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1379300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1371200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1231500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1020600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>988900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>859600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>878100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>772800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>768600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>637500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>633800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>649600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>640100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>656000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>643000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>648000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>667600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>649200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>654100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>678200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>688400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>333800</v>
+      </c>
+      <c r="E10" s="3">
         <v>313600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>326900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>303600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>436400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>386500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>397900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>424200</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>388800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>376400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>418700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>345700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>321200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>326300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>320600</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>273900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>251200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>213100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>214900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>203200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>219300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>186000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>184300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>187100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>185500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>163400</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>192500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>197200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>192700</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1254,8 +1267,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,98 +1374,101 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-300</v>
+      </c>
+      <c r="E14" s="3">
         <v>16600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-31800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-21800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>11700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-1200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>11200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>23800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>4500</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>13900</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>3800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1400</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>38200</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-3000</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>12100</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
       <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>54000</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>900</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
         <v>0</v>
       </c>
@@ -1462,112 +1481,118 @@
       <c r="AJ14" s="3">
         <v>0</v>
       </c>
+      <c r="AK14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>128200</v>
+      </c>
+      <c r="E15" s="3">
         <v>123600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>124600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>127500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>137900</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>126000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>122100</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>116000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>117400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>105000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>93100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>79200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>80800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>77800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>79200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>78500</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>96500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>85700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>83300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>84700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>86500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>80400</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>79500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>79200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>85300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>78800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>78500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>78600</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>80800</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>77200</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>73000</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>71100</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>77500</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,216 +1626,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1320100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1348000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1383200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1383800</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1448000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1503000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1619100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1619000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1518900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1479300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1371600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1133400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1099000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>980300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>930400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>847200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>945500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>723100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>742400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>730000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>563200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>782200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>765300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>810800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>779400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>794000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>864000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>843600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>917300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>901900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>856800</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>846000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>845700</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>97600</v>
+      </c>
+      <c r="E18" s="3">
         <v>73900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>72100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>36500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>166100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>122200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>138500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>172100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>249200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>268300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>278600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>232900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>211100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>205600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>268300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>199500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>74300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>127500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>106300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>122800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>296200</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>59800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>62000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>24300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>73700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>18600</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>31800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>35200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>34400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>38100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>32500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>35400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,528 +1879,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-35200</v>
+      </c>
+      <c r="E20" s="3">
         <v>-11300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-47500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-90100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-8600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-59600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-223000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-106200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-5900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>600</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>-900</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>1400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>20500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>13000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>93100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>9000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>34900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>261000</v>
+      </c>
+      <c r="E21" s="3">
         <v>208700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>244200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>254100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>312600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>307800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>483600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>394400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>360700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>372300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>369300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>311700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>291200</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>284100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>347500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>277100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>169700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>210900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>187700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>208200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>384100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>137500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>139200</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>124000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>155700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>92400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>74000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>203500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>125000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>114700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>113500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>102000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>147800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54900</v>
+      </c>
+      <c r="E22" s="3">
         <v>66800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>69200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>62900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>68500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>70300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>70200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>50300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>46100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>39800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>24000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>15600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>16400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>18800</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>17900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>19100</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>18600</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>20900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20200</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20100</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>23000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22300</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>21700</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E23" s="3">
         <v>1600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>82100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>85500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>94500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>112700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>295900</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>216800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>197200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>227500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>252200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>216800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>195400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>190800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>253000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>182100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>56400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>106400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>86400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>104400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>279000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>37700</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>38800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>24900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>50200</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>101800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>21900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>15000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>18100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>9200</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>47900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-17500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>7200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-15400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>40700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>38000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>35200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>47300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26100</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>37800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>42600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>55000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>28700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>10200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>19900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>18300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>35600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10900</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>7800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>5300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>9700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>6300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>7700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>6200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,216 +2519,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>103800</v>
+      </c>
+      <c r="E26" s="3">
         <v>19100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>81400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>81600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>87300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>128100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>255200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>189900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>159200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>192300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>204800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>190700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>157600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>148200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>198100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>153400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>46100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>101600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>66500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>86100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>243400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>26800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>31000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>19600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>40400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>98100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>70200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>8700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>10300</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7400</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>41700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E27" s="3">
         <v>16900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>78900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>81200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>84500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>125000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>252400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>185800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>156600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>191100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>202000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>188100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>155800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>146800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>196600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>151800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>44700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>101100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>65400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>85500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>242600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>25700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>26300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>18000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>38900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>97300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>69000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>40500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2839,8 +2899,8 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2857,11 +2917,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2869,11 +2929,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,216 +3161,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>35200</v>
+      </c>
+      <c r="E32" s="3">
         <v>11300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>47500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>90100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>8600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>59600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>223000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>106200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>5900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-600</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>900</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-1400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2800</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>5100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1600</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E33" s="3">
         <v>16900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>78900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>81200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>84500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>125000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>252400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>185800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>156600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>191100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>202000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>188100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>155800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>146800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>196600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>151800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>44700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>101100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>65400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>85500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>242600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>25700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>26300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>18000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>40600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>97300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>105700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>40500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,221 +3482,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E35" s="3">
         <v>16900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>78900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>81200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>84500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>125000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>252400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>185800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>156600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>191100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>202000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>188100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>155800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>146800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>196600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>151800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>44700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>101100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>65400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>85500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>242600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>25700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>26300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>18000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>40600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>97300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>105700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>40500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45290</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44562</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44198</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43827</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43463</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43099</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,112 +3781,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E41" s="3">
         <v>114800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>121600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>145500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>126500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>119000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>111500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>132600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>127000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>146700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>99500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>68900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>67200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>77700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>71200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>81600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>65800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>76200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>72900</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>69100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>87000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>95700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>107300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>81500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>104100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>122900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>106800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>110100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>124800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>138900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>114600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3904,736 +3993,760 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>625600</v>
+      </c>
+      <c r="E43" s="3">
         <v>616700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>611300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>656400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>821900</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>761300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>769300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>795900</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>695200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>687300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>602100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>542800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>470200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>482600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>436100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>388900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>409300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>377500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>379700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>400800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>409700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>360000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>363200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>375400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>392200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>371700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>378300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>418400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>396400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>420300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>389300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>396800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>395900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>576800</v>
+      </c>
+      <c r="E44" s="3">
         <v>617800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>627700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>687500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>758700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>822800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>825100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>828800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>673600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>642000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>578400</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>491700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>457500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>476300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>428200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>420700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>405900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>406800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>394700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>381400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>363000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>353000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>348300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>339900</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>341000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>361700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>370600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>373100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>358200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>375100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>359600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>342100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>330800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>42100</v>
+      </c>
+      <c r="E45" s="3">
         <v>23600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>31900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>28200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>38100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>53200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>36200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>142300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>106700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>134600</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>125000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>92500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>77500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>80600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>60000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>90200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>81000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>80500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>71500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>71700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>71600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>68600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>60100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>57500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>63700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>65300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>56700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>95100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>56700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>51100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>49500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>52000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1439400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1496900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1507500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1619300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1855700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1843000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1876000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1902500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1638100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1562000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1461800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1259000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1089000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1103600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1022600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>940800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>987000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>931200</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>931100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>930100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>917300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>853700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>867100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>871200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>897900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>878500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>918200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>971100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>956400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>962200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>924900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>927300</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>893300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2263700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2332000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2415500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2378500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2251600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2164200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2214300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2125100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1926400</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1814600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1736200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1563800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1349200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1107800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1037400</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>915100</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>804700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>742900</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>729100</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>802200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>689400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>447700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>458000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>433400</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>410200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>398800</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>399100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>409100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>302000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>290000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>279800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>270900</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>292700</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2924400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3069700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3050800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3126200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3140700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3001700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2971100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2901800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2648200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2520800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2414500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2033000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1995500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1995300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2011800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1967300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2010400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1931400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1908200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1888000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1927100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1833800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1843200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1821300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3221000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3433300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3410800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3555600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3560400</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3538800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3640800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3678700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2835500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2773900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2315900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1646200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1616900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1649600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1684600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1693800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1733900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1714100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1702300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="W49" s="3">
-        <v>1749700</v>
       </c>
       <c r="X49" s="3">
         <v>1749700</v>
       </c>
       <c r="Y49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="Z49" s="3">
         <v>1799500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,112 +4956,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>199600</v>
+      </c>
+      <c r="E52" s="3">
         <v>222100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>218800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>246600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>235000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>238100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>246000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>232000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>154200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>137500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>98200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>113600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>83000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>69300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>76900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>74500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>77400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>61400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>56500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>57200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>61800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>60000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>68700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>67500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>70100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>71400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>78200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>76300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>64200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>65300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>57800</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10070500</v>
+      </c>
+      <c r="E54" s="3">
         <v>10572700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10620600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10942800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>11061100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10810300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10973200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10861100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>9202400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>8808800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8026700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6615600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6133700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>5925700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5833300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5591400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5613300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5381000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5327200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5377800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5345300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>4944900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5036600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4995100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>348700</v>
+      </c>
+      <c r="E57" s="3">
         <v>331700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>349500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>343400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>425600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>394700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>427100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>433800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>472500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>398200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>414600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>351300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>307100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>272800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>264400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>245600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>255300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>207000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>197500</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>211600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>239300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>192000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>208900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>192500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>219500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>177800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>185200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>188000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>217400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>213600</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>186500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>181400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>180900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>195800</v>
+      </c>
+      <c r="E58" s="3">
         <v>174000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>150100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>162600</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>116000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>126200</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>136500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>164200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>69800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>63700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>32700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>35300</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>24400</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>55100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>41600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>27000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>26200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>42800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>86400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>91000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>61100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>35900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>23700</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>7500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>11100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>16700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>18200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>19400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>25000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>23200</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>77200</v>
+      </c>
+      <c r="E59" s="3">
         <v>92300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>15500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>18300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>29800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>38400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>526100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>566100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>472500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>426800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>421200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>428200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>386200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>365100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>392400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>390400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>366000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>353800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>358100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>342800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>321500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>330000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>313500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>297000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>290100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>302100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>325900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>314500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>283200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>245400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>247700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1043500</v>
+      </c>
+      <c r="E60" s="3">
         <v>1062500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>963100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>967300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>998100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1033700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1013500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1099000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1068400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1028000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>919800</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>813400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>752700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>756200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>692200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>637700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>675300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>623600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>606300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>651700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>688300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>595900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>566300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>546200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>540500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>485800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>482700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>506900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>559500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>546300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>489000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>451800</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>451900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4061300</v>
+      </c>
+      <c r="E61" s="3">
         <v>4290300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4473600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4524200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4521300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4493000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4608000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4703200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3315000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3220900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2881100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1677900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1439000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1325700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1393800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1417500</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1480500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1448000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1553100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1664900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1558400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1559800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1640100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1663800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>190700</v>
+      </c>
+      <c r="E62" s="3">
         <v>189600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>219900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>283400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>329100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>291800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>316600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>391900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>922500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>891100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>659200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>628600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>594300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>574600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>563500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>506300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>503300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>474200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>469400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>452700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>455100</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>416300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>423600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>428400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>346100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>335900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>348300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>375000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>373000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>449400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>446100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>436500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>442200</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5606200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5938400</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6078000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6259800</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6367400</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6343400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6522700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6739500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5393300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5228600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>4533200</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3190300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>2852800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2720200</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2714700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2624800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2721400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2607100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2693800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2834200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2779400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2636400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2693700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2704500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4012100</v>
+      </c>
+      <c r="E72" s="3">
         <v>3910200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3893300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3814400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3733300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3648700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3523700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3271300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3085500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2929000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2737900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2535900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2347800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2192100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2045300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1848700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1696900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1652200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1551100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1485600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1400100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1157500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1131800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1105500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>981200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>875500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>867700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>858600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>852800</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4377800</v>
+      </c>
+      <c r="E76" s="3">
         <v>4551400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4460900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4593100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4605400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4380700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4368200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4032500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>3809000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3580100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3493500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3425300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3281000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3205500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3118600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2966600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2891900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2773900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2633400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2543600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2565800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2308500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2342900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2290500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,221 +7534,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45654</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45290</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44562</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44198</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43827</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43463</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43099</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>101900</v>
+      </c>
+      <c r="E81" s="3">
         <v>16900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>78900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>81200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>84500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>125000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>252400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>185800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>156600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>191100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>202000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>188100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>155800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>146800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>196600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>151800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>44700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>101100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>65400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>85500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>242600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>25700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>26300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>18000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>40600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>97300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>105700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>40500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E83" s="3">
         <v>93800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>88700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>89900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>91500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>72100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>62700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>117400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>105000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>93100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>79200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>77800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>79200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>78500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>96500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>85700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>83300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>84700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>86500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>80400</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>79500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>79200</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>85300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>78800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>78500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>78600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>80800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>77200</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>73000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>71100</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>77500</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,112 +8434,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>154400</v>
+      </c>
+      <c r="E89" s="3">
         <v>274500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>146500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>263900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>217000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>276600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>217300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>188400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>175300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>277400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>208800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>152200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>252400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>154100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>159100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>138800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>154200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>206800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>229100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>34500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>99900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>108400</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>105700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>48600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>198900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>71700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>101100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>26900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>141800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>71200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>103100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>94500</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>110500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,112 +8582,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-67400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-98000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-93800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-174900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-146200</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-123000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-111300</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-134200</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-105600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-79900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-71600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-82400</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-60800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-95200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="U91" s="3">
-        <v>-61600</v>
       </c>
       <c r="V91" s="3">
         <v>-61600</v>
       </c>
       <c r="W91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="X91" s="3">
         <v>-114400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-77200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-83600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-84300</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,112 +8901,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-46300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-64900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-96700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-291000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-168800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-158300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-91600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-193800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-598000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-294500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-270500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-89800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-65600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-64300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-123300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-61500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-61200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-64600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-103200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-72100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-83000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8843,8 +9076,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8921,8 +9154,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,316 +9475,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-166300</v>
+      </c>
+      <c r="E100" s="3">
         <v>-201000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-81000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>48800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-25900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-117900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-152700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1172800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-4300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>325300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1176700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>180900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>18700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-69200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-89800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-81000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-19500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-159500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-168400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>40400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>5300</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-49200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-32100</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>21200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>46200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-11400</v>
+      </c>
+      <c r="E101" s="3">
         <v>9000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>7300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>25600</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4200</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-7900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>25600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>1200</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>2900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-3800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>3900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>300</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-6900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1700</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>5100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>3900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>10900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>300</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-43600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-27000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>28200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>10900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>9400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-17700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>111700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2800</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>47300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>30500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-10600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>6500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>15800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-17800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-8700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>25800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>16100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>24300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,476 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="20" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45654</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45290</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44562</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44198</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43827</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43463</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43099</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1380600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1417700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1421900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1455300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1420300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1614100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1625200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1757600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1791200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1768100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1747600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1650200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1366300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1310100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1185900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1198700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1046700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1019800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>850600</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>848700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>852800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>859400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>842000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>827300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>835100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>853100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>812600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>846600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>875400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>952500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>936300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>894900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>878500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>881100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1069200</v>
+      </c>
+      <c r="E9" s="3">
         <v>1083900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1108300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1128400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1116700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1177700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1238700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1359700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1367000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1379300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1371200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1231500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1020600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>988900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>859600</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>878100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>772800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>768600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>637500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>633800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>649600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>640100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>656000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>643000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>648000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>667600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>649200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>654100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>678200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>688400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>311400</v>
+      </c>
+      <c r="E10" s="3">
         <v>333800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>313600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>326900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>303600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>436400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>386500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>397900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>424200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>388800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>376400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>418700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>345700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>321200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>326300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>320600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>273900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>251200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>213100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>214900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>203200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>219300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>186000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>184300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>187100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>185500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>163400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>192500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>197200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>192700</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1270,8 +1284,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,101 +1394,104 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7000</v>
+      </c>
+      <c r="E14" s="3">
         <v>-300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>16600</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-31800</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-21800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>11700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-1200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-4600</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>23800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>4500</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>13900</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>3800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1400</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>38200</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3">
         <v>12100</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>54000</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>900</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
       <c r="AH14" s="3">
         <v>0</v>
       </c>
@@ -1484,115 +1504,121 @@
       <c r="AK14" s="3">
         <v>0</v>
       </c>
+      <c r="AL14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E15" s="3">
         <v>128200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>123600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>124600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>127500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>137900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>126000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>122100</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>116000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>117400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>105000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>93100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>79200</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>80800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>77800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>79200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>78500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>96500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>85700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>83300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>84700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>86500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>80400</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>79500</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>79200</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>85300</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>78800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>78500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>78600</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>80800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>77200</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>73000</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>77500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1315100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1320100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1348000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1383200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1383800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1448000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1503000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1619100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1619000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1518900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1479300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1371600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1133400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1099000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>980300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>930400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>847200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>945500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>723100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>742400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>730000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>563200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>782200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>765300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>810800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>779400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>794000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>864000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>843600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>917300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>901900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>856800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>846000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>845700</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>65500</v>
+      </c>
+      <c r="E18" s="3">
         <v>97600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>73900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>72100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>36500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>166100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>122200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>138500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>172100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>249200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>268300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>278600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>232900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>211100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>205600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>268300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>199500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>74300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>127500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>106300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>122800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>296200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>59800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>62000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>24300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>73700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>18600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>31800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>35200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>34400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>38100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>32500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>35400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,543 +1913,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>25500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-35200</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-11300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-47500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-90100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-59600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-223000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-106200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-5900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>600</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>-900</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-2300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>1400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2800</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>20500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>13000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>93100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>9000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2400</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>34900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>163900</v>
+      </c>
+      <c r="E21" s="3">
         <v>261000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>208700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>244200</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>254100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>312600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>307800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>483600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>394400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>360700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>372300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>369300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>311700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>291200</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>284100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>347500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>277100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>169700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>210900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>187700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>208200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>384100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>137500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>139200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>124000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>155700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>92400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>74000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>203500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>125000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>114700</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>113500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>102000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>147800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>58000</v>
+      </c>
+      <c r="E22" s="3">
         <v>54900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>66800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>69200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>62900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>68500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>70300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>70200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>50300</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>46100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>39800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>24000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>16400</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>18800</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>17900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>19100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18600</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>19400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>20900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>20200</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20100</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>23000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23100</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>22400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>21700</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>22400</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E23" s="3">
         <v>78200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>82100</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>85500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>94500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>112700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>295900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>216800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>197200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>227500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>252200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>216800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>195400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>190800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>253000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>182100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>56400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>106400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>86400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>104400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>279000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>37700</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>38800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>24900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>50200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>101800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>21900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>15000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>18100</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>9200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>47900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E24" s="3">
         <v>-25500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-17500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>7200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-15400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>40700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>38000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>35200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>47300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>26100</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>37800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>42600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>55000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>28700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>10200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>19900</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>18300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>35600</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>10900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>7800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>5300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>9700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>6300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>7700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6200</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-23800</v>
+      </c>
+      <c r="E26" s="3">
         <v>103800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>19100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>81400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>81600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>87300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>128100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>255200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>189900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>159200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>192300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>204800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>190700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>157600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>148200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>198100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>153400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>46100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>101600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>66500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>86100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>243400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>26800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>31000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>19600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>40400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>98100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>70200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>8700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>10300</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>41700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E27" s="3">
         <v>101900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>16900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>78900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>81200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>84500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>125000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>252400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>185800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>156600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>191100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>202000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>188100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>155800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>146800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>196600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>151800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>44700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>101100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>65400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>85500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>242600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>25700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>26300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>18000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>38900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>97300</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>69000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>40500</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2902,8 +2963,8 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2920,11 +2981,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2932,11 +2993,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-25500</v>
+      </c>
+      <c r="E32" s="3">
         <v>35200</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>11300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>47500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>90100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>59600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>223000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>106200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>5900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-600</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>900</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>2300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2800</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2300</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>5100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E33" s="3">
         <v>101900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>16900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>78900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>81200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>84500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>125000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>252400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>185800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>156600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>191100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>202000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>188100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>155800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>146800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>196600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>151800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>44700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>101100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>65400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>85500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>242600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>25700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>26300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>18000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>40600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>97300</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>105700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>40500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E35" s="3">
         <v>101900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>16900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>78900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>81200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>84500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>125000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>252400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>185800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>156600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>191100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>202000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>188100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>155800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>146800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>196600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>151800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>44700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>101100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>65400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>85500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>242600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>25700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>26300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>18000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>40600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>97300</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>105700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>40500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45654</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45290</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44562</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44198</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43827</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43463</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43099</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,115 +3868,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>81500</v>
+      </c>
+      <c r="E41" s="3">
         <v>76000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>114800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>121600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>145500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>126500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>119000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>111500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>132600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>127000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>126000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>146700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>99500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>68900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>67200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>77700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>71200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>81600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>65800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>76200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>76300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>72900</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>69100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>87000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>95700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>107300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>81500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>104100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>122900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>106800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>110100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>124800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>138900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>114600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3996,757 +4086,781 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>622200</v>
+      </c>
+      <c r="E43" s="3">
         <v>625600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>616700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>611300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>656400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>821900</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>761300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>769300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>795900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>695200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>687300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>602100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>542800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>470200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>482600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>436100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>388900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>409300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>377500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>379700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>400800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>409700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>360000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>363200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>375400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>392200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>371700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>378300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>418400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>396400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>420300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>389300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>396800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>395900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>595400</v>
+      </c>
+      <c r="E44" s="3">
         <v>576800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>617800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>627700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>687500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>758700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>822800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>825100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>828800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>673600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>642000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>578400</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>491700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>457500</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>476300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>428200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>420700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>405900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>406800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>394700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>381400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>363000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>353000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>348300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>339900</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>341000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>361700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>370600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>373100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>358200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>375100</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>359600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>342100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>330800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>25900</v>
+      </c>
+      <c r="E45" s="3">
         <v>42100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>23600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>31900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>28200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>38100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>53200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>36200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>142300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>106700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>134600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>125000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>92500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>77500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>80600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>60000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>90200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>81000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>80500</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>71500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>71700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>71600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>68600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>60100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>57500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>63700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>65300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>56700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>95100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>56700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>51100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>49500</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>52000</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1454700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1439400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1496900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1507500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1619300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1855700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1843000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1876000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1902500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1638100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1562000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1461800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1259000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1089000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1103600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1022600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>940800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>987000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>931200</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>931100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>930100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>917300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>853700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>867100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>871200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>897900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>878500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>918200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>971100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>956400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>962200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>924900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>927300</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>893300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2111700</v>
+      </c>
+      <c r="E47" s="3">
         <v>2263700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2332000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2415500</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2378500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2251600</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2164200</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2214300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2125100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1926400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1814600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1736200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1563800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1349200</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1107800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1037400</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>915100</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>804700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>742900</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>729100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>802200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>689400</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>447700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>458000</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>433400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>410200</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>398800</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>399100</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>409100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>302000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>290000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>279800</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>270900</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>292700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2957000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2924400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3069700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3050800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3126200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3140700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3001700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2971100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2901800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2648200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2520800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2414500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2033000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1995500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1995300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2011800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1967300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>2010400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1931400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1908200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1888000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1927100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1833800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1843200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1821300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3287300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3221000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3433300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3410800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3555600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3560400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3538800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3640800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3678700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2835500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2773900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2315900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1646200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1616900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1649600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1684600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1693800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1733900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1714100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1702300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="X49" s="3">
-        <v>1749700</v>
       </c>
       <c r="Y49" s="3">
         <v>1749700</v>
       </c>
       <c r="Z49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="AA49" s="3">
         <v>1799500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,115 +5076,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>203100</v>
+      </c>
+      <c r="E52" s="3">
         <v>199600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>222100</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>218800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>246600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>235000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>238100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>246000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>232000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>154200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>137500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>98200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>113600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>83000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>69300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>76900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>74500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>77400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>61400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>56500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>57200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>61800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>60000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>68700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>67500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>68400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>70100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>71400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>78200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>76300</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>64200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>65300</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>57800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>58600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10032000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10070500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10572700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10620600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10942800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>11061100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10810300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10973200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10861100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>9202400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>8808800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8026700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6615600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6133700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>5925700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5833300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5591400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5613300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5381000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5327200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5377800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5345300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>4944900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5036600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>4995100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>348500</v>
+      </c>
+      <c r="E57" s="3">
         <v>348700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>331700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>349500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>343400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>425600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>394700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>427100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>433800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>472500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>398200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>414600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>351300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>307100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>272800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>264400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>245600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>255300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>207000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>197500</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>211600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>239300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>192000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>208900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>192500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>219500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>177800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>185200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>188000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>217400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>213600</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>186500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>181400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>180900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E58" s="3">
         <v>195800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>174000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>150100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>162600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>116000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>126200</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>136500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>164200</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>69800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>63700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>32700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>35300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>24400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>55100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>41600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>26200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>42800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>86400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>91000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>61100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>35900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>23700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>7500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>11100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>16700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>18200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>19400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>25000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>23200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>90600</v>
+      </c>
+      <c r="E59" s="3">
         <v>77200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>92300</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>11700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>15500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>29800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>38400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>526100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>566100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>472500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>426800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>421200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>428200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>386200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>365100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>392400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>390400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>366000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>353800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>358100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>342800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>321500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>330000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>313500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>297000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>290100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>302100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>325900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>314500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>283200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>245400</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>247700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1035800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1043500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1062500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>963100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>967300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>998100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1033700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1013500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1099000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1068400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1028000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>919800</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>813400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>752700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>756200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>692200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>637700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>675300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>623600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>606300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>651700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>688300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>595900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>566300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>546200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>540500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>485800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>482700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>506900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>559500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>546300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>489000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>451800</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>451900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3963300</v>
+      </c>
+      <c r="E61" s="3">
         <v>4061300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4290300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4473600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4524200</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4521300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4493000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4608000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4703200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3315000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3220900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2881100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1677900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1439000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1325700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1393800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1417500</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1480500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1448000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1553100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1664900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1558400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1559800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1640100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1663800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>189200</v>
+      </c>
+      <c r="E62" s="3">
         <v>190700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>189600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>219900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>283400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>329100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>291800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>316600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>391900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>922500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>891100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>659200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>628600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>594300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>574600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>563500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>506300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>503300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>474200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>469400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>452700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>455100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>416300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>423600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>428400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>346100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>335900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>348300</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>375000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>373000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>449400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>446100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>436500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>442200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5496300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5606200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5938400</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6078000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6259800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6367400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6343400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6522700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6739500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5393300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5228600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>4533200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3190300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2852800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2720200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2714700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2624800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2721400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2607100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2693800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2834200</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2779400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2636400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2693700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2704500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3986000</v>
+      </c>
+      <c r="E72" s="3">
         <v>4012100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3910200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3893300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3814400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3733300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3648700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3523700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3271300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3085500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2929000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2737900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2535900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2347800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2192100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2045300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1848700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1696900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1652200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1551100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1485600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1400100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1157500</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1131800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1105500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>981200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>875500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>867700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>858600</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>852800</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4448400</v>
+      </c>
+      <c r="E76" s="3">
         <v>4377800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4551400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4460900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4593100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4605400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4380700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4368200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4032500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>3809000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3580100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3493500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3425300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3281000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3205500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3118600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2966600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2891900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2773900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2633400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2543600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2565800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2308500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2342900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2290500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45654</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45290</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44562</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44198</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43827</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43463</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43099</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-26200</v>
+      </c>
+      <c r="E81" s="3">
         <v>101900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>16900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>78900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>81200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>84500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>125000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>252400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>185800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>156600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>191100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>202000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>188100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>155800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>146800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>196600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>151800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>44700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>101100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>65400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>85500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>242600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>25700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>26300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>18000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>40600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>97300</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>105700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>40500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>99500</v>
+      </c>
+      <c r="E83" s="3">
         <v>104800</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>93800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>88700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>89900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>91500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>72100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>62700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>117400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>105000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>93100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>79200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>77800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>79200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>78500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>96500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>85700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>83300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>84700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>86500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>80400</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>79500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>79200</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>85300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>78800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>78500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>78600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>80800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>77200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>73000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>71100</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>77500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>249000</v>
+      </c>
+      <c r="E89" s="3">
         <v>154400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>274500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>146500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>263900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>217000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>276600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>217300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>188400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>175300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>277400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>208800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>152200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>252400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>154100</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>159100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>138800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>154200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>206800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>229100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>34500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>99900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>108400</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>105700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>48600</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>198900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>71700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>101100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>26900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>141800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>71200</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>103100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>94500</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>110500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-63000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-73300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-67400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-98000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-93800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-174900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-146200</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-123000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-111300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-134200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-105600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-79900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-71600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-82400</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-60800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-95200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="V91" s="3">
-        <v>-61600</v>
       </c>
       <c r="W91" s="3">
         <v>-61600</v>
       </c>
       <c r="X91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="Y91" s="3">
         <v>-114400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-77200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-84300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-50700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-46300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-64900</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-96700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-291000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-168800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-158300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-91600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-193800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-598000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-294500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-270500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-89800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-65600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-64300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-123300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-61500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-61200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-103200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-72100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9079,8 +9313,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9157,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-185200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-166300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-201000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-81000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>48800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-25900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-117900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-152700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1172800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-4300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>325300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1176700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>180900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>18700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-69200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-89800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-81000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-19500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-159500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-168400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>40400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>5300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-49200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-32100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>21200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>46200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11400</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>9000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9300</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>7300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>25600</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-4200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7900</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>25600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>1200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-5600</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>2900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>3900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>300</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-6900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>3900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>10900</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>300</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>6900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-43600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-27000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>28200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>10900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>9400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-17700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>111700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>47300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>30500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-10600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>6500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-10300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>15800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-17800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>25800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>16100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>24300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,489 +656,502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="21" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="22" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45654</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45290</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44562</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44198</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43827</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43463</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43099</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1481500</v>
+      </c>
+      <c r="E8" s="3">
         <v>1380600</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1417700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1421900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1455300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1420300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1614100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1625200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1757600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1791200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1768100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1747600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1650200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1366300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1310100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1185900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1198700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1046700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1019800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>850600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>848700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>852800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>859400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>842000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>827300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>835100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>853100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>812600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>846600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>875400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>952500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>936300</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>894900</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>878500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>881100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1135600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1069200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1083900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1108300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1128400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1116700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1177700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1238700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1359700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1367000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1379300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1371200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1231500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1020600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>988900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>859600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>878100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>772800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>768600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>637500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>633800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>649600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>640100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>656000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>643000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>648000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>667600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>649200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>654100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>678200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>688400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>345900</v>
+      </c>
+      <c r="E10" s="3">
         <v>311400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>333800</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>313600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>326900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>303600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>436400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>386500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>397900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>424200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>388800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>376400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>418700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>345700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>321200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>326300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>320600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>273900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>251200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>213100</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>214900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>203200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>219300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>186000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>184300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>187100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>185500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>163400</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>192500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>197200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>192700</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1287,8 +1301,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1397,104 +1414,107 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E14" s="3">
         <v>7000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>-300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>16600</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-31800</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21800</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>11700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-1200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>23800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>4500</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>13900</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>3800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1400</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>38200</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
         <v>12100</v>
       </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>54000</v>
       </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>900</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
       <c r="AI14" s="3">
         <v>0</v>
       </c>
@@ -1507,118 +1527,124 @@
       <c r="AL14" s="3">
         <v>0</v>
       </c>
+      <c r="AM14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>121100</v>
+      </c>
+      <c r="E15" s="3">
         <v>123800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>128200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>124600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>127500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>137900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>126000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>122100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>116000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>117400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>105000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>93100</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>79200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>80800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>77800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>79200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>78500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>96500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>85700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>83300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>84700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>86500</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>80400</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>79500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>79200</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>85300</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>78800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>78500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>78600</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>80800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>77200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>71100</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>77500</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,228 +1680,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1400900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1315100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1320100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1348000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1383200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1383800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1448000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1503000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1619100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1619000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1518900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1479300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1371600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1133400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1099000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>980300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>930400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>847200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>945500</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>723100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>742400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>730000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>563200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>782200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>765300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>810800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>779400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>794000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>864000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>843600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>917300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>901900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>856800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>846000</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>845700</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E18" s="3">
         <v>65500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>97600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>73900</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>72100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>36500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>166100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>122200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>138500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>172100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>249200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>268300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>278600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>232900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>211100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>205600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>268300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>199500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>74300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>127500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>106300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>122800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>296200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>59800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>62000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>24300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>73700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>18600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>31800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>35200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>34400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>38100</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>32500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>35400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,558 +1947,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>25500</v>
+        <v>-6500</v>
       </c>
       <c r="E20" s="3">
+        <v>33100</v>
+      </c>
+      <c r="F20" s="3">
         <v>-35200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-11300</v>
       </c>
-      <c r="G20" s="3">
-        <v>-47500</v>
-      </c>
       <c r="H20" s="3">
-        <v>-90100</v>
+        <v>-45700</v>
       </c>
       <c r="I20" s="3">
+        <v>-83500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-8600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-59600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-223000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-106200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-5900</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>600</v>
       </c>
-      <c r="S20" s="3">
-        <v>0</v>
-      </c>
       <c r="T20" s="3">
+        <v>0</v>
+      </c>
+      <c r="U20" s="3">
         <v>-900</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-1100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-2000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>1400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>20500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>13000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>93100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>9000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>34900</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>163900</v>
+        <v>208200</v>
       </c>
       <c r="E21" s="3">
+        <v>156300</v>
+      </c>
+      <c r="F21" s="3">
         <v>261000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>208700</v>
       </c>
-      <c r="G21" s="3">
-        <v>244200</v>
-      </c>
       <c r="H21" s="3">
-        <v>254100</v>
+        <v>242400</v>
       </c>
       <c r="I21" s="3">
+        <v>247500</v>
+      </c>
+      <c r="J21" s="3">
         <v>312600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>307800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>483600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>394400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>360700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>372300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>369300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>311700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>291200</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>284100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>347500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>277100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>169700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>210900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>187700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>208200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>384100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>137500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>139200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>124000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>155700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>92400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>74000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>203500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>125000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>114700</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>113500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>102000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>147800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>51900</v>
+      </c>
+      <c r="E22" s="3">
         <v>58000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>54900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>66800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>69200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>62900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>68500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>70300</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>70200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>50300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>46100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>39800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>24000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15400</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>16400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>16900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>18800</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>17900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>19100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18600</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>20900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20200</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20100</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>23000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>23100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22300</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>22500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>22400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>21700</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>22400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E23" s="3">
         <v>-25000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>78200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>1600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>82100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>85500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>94500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>112700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>295900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>216800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>197200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>227500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>252200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>216800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>195400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>190800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>253000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>182100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>56400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>106400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>86400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>104400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>279000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>37700</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>38800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>24900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>50200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>101800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>21900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>15000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>18100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>9200</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>47900</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-25500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-17500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>7200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-15400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>40700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>38000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>35200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>47300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>26100</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>37800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>42600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>55000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>28700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>10200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>19900</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>18300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>35600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>10900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>7800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>5300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>9700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>6300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6200</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,228 +2623,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-23800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>103800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>19100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>81400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>81600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>87300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>128100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>255200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>189900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>159200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>192300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>204800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>190700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>157600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>148200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>198100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>153400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>46100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>101600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>66500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>86100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>243400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>26800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>31000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>19600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>40400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>98100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>70200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>8700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>10300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7400</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>41700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-26200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>101900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>78900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>81200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>84500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>125000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>252400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>185800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>156600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>191100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>202000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>188100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>155800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>146800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>196600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>151800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>44700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>101100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>65400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>85500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>242600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>25700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>26300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>18000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>38900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>97300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>69000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>40500</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2966,8 +3027,8 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2984,11 +3045,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2996,11 +3057,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,228 +3301,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-25500</v>
+        <v>6500</v>
       </c>
       <c r="E32" s="3">
+        <v>-33100</v>
+      </c>
+      <c r="F32" s="3">
         <v>35200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>11300</v>
       </c>
-      <c r="G32" s="3">
-        <v>47500</v>
-      </c>
       <c r="H32" s="3">
-        <v>90100</v>
+        <v>45700</v>
       </c>
       <c r="I32" s="3">
+        <v>83500</v>
+      </c>
+      <c r="J32" s="3">
         <v>8600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>59600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>223000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>106200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>5900</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-600</v>
       </c>
-      <c r="S32" s="3">
-        <v>0</v>
-      </c>
       <c r="T32" s="3">
+        <v>0</v>
+      </c>
+      <c r="U32" s="3">
         <v>900</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>1100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>2000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2800</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>5100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1600</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-26200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>101900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>78900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>81200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>84500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>125000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>252400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>185800</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>156600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>191100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>202000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>188100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>155800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>146800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>196600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>151800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>44700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>101100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>65400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>85500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>242600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>25700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>26300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>18000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>40600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>97300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>105700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>40500</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,233 +3640,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-26200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>101900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>78900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>81200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>84500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>125000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>252400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>185800</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>156600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>191100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>202000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>188100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>155800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>146800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>196600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>151800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>44700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>101100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>65400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>85500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>242600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>25700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>26300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>18000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>40600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>97300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>105700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>40500</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45654</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45290</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44562</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44198</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43827</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43463</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43099</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,123 +3955,127 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>94600</v>
+      </c>
+      <c r="E41" s="3">
         <v>81500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>76000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>114800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>121600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>145500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>126500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>119000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>111500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>132600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>127000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>126000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>146700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>68900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>67200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>77700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>71200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>81600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>65800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>76200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>76300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>72900</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>69100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>87000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>95700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>107300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>81500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>104100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>122900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>106800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>110100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>124800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>138900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>114600</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -4089,778 +4179,802 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>639100</v>
+      </c>
+      <c r="E43" s="3">
         <v>622200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>625600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>616700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>611300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>656400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>821900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>761300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>769300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>795900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>695200</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>687300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>602100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>542800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>470200</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>482600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>436100</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>388900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>409300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>377500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>379700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>400800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>409700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>360000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>363200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>375400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>392200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>371700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>378300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>418400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>396400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>420300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>389300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>396800</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>395900</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>605300</v>
+      </c>
+      <c r="E44" s="3">
         <v>595400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>576800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>617800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>627700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>687500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>758700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>822800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>825100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>828800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>673600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>642000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>578400</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>491700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>457500</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>476300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>428200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>420700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>405900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>406800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>394700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>381400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>363000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>353000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>348300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>339900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>341000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>361700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>370600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>373100</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>358200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>375100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>359600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>342100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>330800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>43200</v>
+      </c>
+      <c r="E45" s="3">
         <v>25900</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>42100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>31900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>28200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>42600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>38100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>53200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>36200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>142300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>106700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>134600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>125000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>92500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>77500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>80600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>60000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>90200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>81000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>80500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>71500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>71700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>71600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>68600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>60100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>57500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>63700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>65300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>56700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>95100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>56700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>51100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>49500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>52000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1495200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1454700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1439400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1496900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1507500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1619300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1855700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1843000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1876000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1902500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1638100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1562000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1461800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1259000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1089000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1103600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1022600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>940800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>987000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>931200</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>931100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>930100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>917300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>853700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>867100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>871200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>897900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>878500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>918200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>971100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>956400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>962200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>924900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>927300</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>893300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2162200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2111700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2263700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2332000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2415500</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2378500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2251600</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2164200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2214300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2125100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1926400</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>1814600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1736200</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1563800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1349200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1107800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1037400</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>915100</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>804700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>742900</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>729100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>802200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>689400</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>447700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>458000</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>433400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>410200</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>398800</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>399100</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>409100</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>302000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>290000</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>279800</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>270900</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>292700</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3019400</v>
+      </c>
+      <c r="E48" s="3">
         <v>2957000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2924400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3069700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>3050800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3126200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3140700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3001700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2971100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2901800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2648200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2520800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2414500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2033000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1995500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1995300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2011800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1967300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2010400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1931400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1908200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1888000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1927100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1833800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1843200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1821300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3376600</v>
+      </c>
+      <c r="E49" s="3">
         <v>3287300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3221000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3433300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3410800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3555600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3560400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3538800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3640800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3678700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2835500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2773900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2315900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1646200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1616900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1649600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1684600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1693800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1733900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1714100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1702300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="Y49" s="3">
-        <v>1749700</v>
       </c>
       <c r="Z49" s="3">
         <v>1749700</v>
       </c>
       <c r="AA49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="AB49" s="3">
         <v>1799500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,118 +5196,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>205300</v>
+      </c>
+      <c r="E52" s="3">
         <v>203100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>199600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>222100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>218800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>246600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>235000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>238100</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>246000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>232000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>154200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>137500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>98200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>113600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>83000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>69300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>76900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>74500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>77400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>61400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>56500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>57200</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>61800</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>60000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>68700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>67500</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>68400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>70100</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>71400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>78200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>76300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>64200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>65300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>57800</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>58600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10275000</v>
+      </c>
+      <c r="E54" s="3">
         <v>10032000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10070500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10572700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10620600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10942800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>11061100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10810300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10973200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10861100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>9202400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8808800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8026700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6615600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6133700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>5925700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>5833300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5591400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5613300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5381000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5327200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5377800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5345300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>4944900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5036600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4995100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>365700</v>
+      </c>
+      <c r="E57" s="3">
         <v>348500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>348700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>331700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>349500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>343400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>425600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>394700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>427100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>433800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>472500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>398200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>414600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>351300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>307100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>272800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>264400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>245600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>255300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>207000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>197500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>211600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>239300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>192000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>208900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>192500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>219500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>177800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>185200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>188000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>217400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>213600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>186500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>181400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>180900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>118300</v>
+      </c>
+      <c r="E58" s="3">
         <v>180500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>195800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>174000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>150100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>162600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>116000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>126200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>136500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>164200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>69800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>63700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>32700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>35300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>55100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>41600</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>26200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>42800</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>86400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>91000</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>61100</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>35900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>23700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>7500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>11100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>16700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>16100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>18200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>19400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>25000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>23200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>94100</v>
+      </c>
+      <c r="E59" s="3">
         <v>90600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>77200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>92300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>13300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>15500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>29800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>38400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>526100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>566100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>472500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>426800</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>421200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>428200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>386200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>365100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>392400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>390400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>366000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>353800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>358100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>342800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>321500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>330000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>313500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>297000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>290100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>302100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>325900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>314500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>283200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>245400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>247700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>996700</v>
+      </c>
+      <c r="E60" s="3">
         <v>1035800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1043500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1062500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>963100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>967300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>998100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1033700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1013500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1099000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1068400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1028000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>919800</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>813400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>752700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>756200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>692200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>637700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>675300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>623600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>606300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>651700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>688300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>595900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>566300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>546200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>540500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>485800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>482700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>506900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>559500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>546300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>489000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>451800</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>451900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4098500</v>
+      </c>
+      <c r="E61" s="3">
         <v>3963300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4061300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4290300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4473600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4524200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4521300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4493000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4608000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4703200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3315000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3220900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2881100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1677900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1439000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1325700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1393800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1417500</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1480500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1448000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1553100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1664900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1558400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1559800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1640100</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1663800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>183700</v>
+      </c>
+      <c r="E62" s="3">
         <v>189200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>190700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>189600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>219900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>283400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>329100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>291800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>316600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>391900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>922500</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>891100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>659200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>628600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>594300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>574600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>563500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>506300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>503300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>474200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>469400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>452700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>455100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>416300</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>423600</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>428400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>346100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>335900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>348300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>375000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>373000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>449400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>446100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>436500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>442200</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5582100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5496300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5606200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5938400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6078000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6259800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6367400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6343400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6522700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6739500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5393300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5228600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>4533200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3190300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2852800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2720200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2714700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2624800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2721400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2607100</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2693800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2834200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2779400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2636400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2693700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2704500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3998600</v>
+      </c>
+      <c r="E72" s="3">
         <v>3986000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4012100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3910200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3893300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3814400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3733300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3648700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3523700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3271300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3085500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2929000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2737900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2535900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2347800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2192100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2045300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1848700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1696900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1652200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1551100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1485600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1400100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1157500</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1131800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1105500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>981200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>875500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>867700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>858600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>852800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4613100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4448400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4377800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4551400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4460900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4593100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4605400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4380700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4368200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4032500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>3809000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>3580100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3493500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3425300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3281000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3205500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3118600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>2966600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>2891900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2773900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2633400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2543600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2565800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2308500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2342900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2290500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,233 +7918,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45654</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45290</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44562</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44198</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43827</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43463</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43099</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>12700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-26200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>101900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>78900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>81200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>84500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>125000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>252400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>185800</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>156600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>191100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>202000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>188100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>155800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>146800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>196600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>151800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>44700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>101100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>65400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>85500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>242600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>25700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>26300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>18000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>40600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>97300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>105700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>9100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>40500</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>96200</v>
+      </c>
+      <c r="E83" s="3">
         <v>99500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>104800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>93800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>88700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>89900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>91500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>79700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>62700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>117400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>105000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>93100</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>79200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>77800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>79200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>78500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>96500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>85700</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>83300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>84700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>86500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>80400</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>79500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>79200</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>85300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>78800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>78500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>78600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>80800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>77200</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>73000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>71100</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>77500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,118 +8868,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>145800</v>
+      </c>
+      <c r="E89" s="3">
         <v>249000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>154400</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>274500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>146500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>263900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>217000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>276600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>188400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>175300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>277400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>208800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>152200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>252400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>154100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>159100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>138800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>154200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>206800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>229100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>34500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>99900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>108400</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>105700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>48600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>198900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>71700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>101100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>26900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>141800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>71200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>103100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>94500</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>110500</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,118 +9024,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-71000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-63000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-73300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-67400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-98000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-93800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-174900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-146200</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-123000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-111300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-134200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-105600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-79900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-71600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-82400</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-65300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-60800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-95200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="W91" s="3">
-        <v>-61600</v>
       </c>
       <c r="X91" s="3">
         <v>-61600</v>
       </c>
       <c r="Y91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="Z91" s="3">
         <v>-114400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-77200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-84300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,118 +9361,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-108700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-50700</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-46300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-96700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-291000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-168800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-158300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-91600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-193800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-598000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-294500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-270500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-89800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-65600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-64300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-123300</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-61500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-61200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-64600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-103200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,8 +9517,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,8 +9550,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9394,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,334 +9967,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-30500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-185200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-166300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-201000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-81000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>48800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-25900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-117900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-152700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>1172800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-4300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>325300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1176700</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>180900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>18700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-69200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-89800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-81000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-19500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-159500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-168400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>40400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>5300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-49200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-32100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>21200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>46200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4100</v>
+      </c>
+      <c r="E101" s="3">
         <v>6500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11400</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>9000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>9300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>7300</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>25600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-4200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-7900</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>25600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-4200</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8100</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>1200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-5600</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>2900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>3900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>300</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-6900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>5100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>3900</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>5400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>10900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>300</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5500</v>
+      </c>
+      <c r="E102" s="3">
         <v>6900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-43600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-4700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-27000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>28200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>10900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>9400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-17700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>111700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>47300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>30500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-10600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>15800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>25800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>16100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>24300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,515 +656,528 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="23" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45654</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45290</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44562</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44198</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43827</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43463</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1709800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1564000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1481500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1380600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1417700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1421900</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1455300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1420300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1614100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1625200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1757600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1791200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1768100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1747600</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1650200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1366300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1310100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1185900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1198700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1046700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1019800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>850600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>848700</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>852800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>859400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>842000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>827300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>835100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>853100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>812600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>846600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>875400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>952500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>936300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>894900</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>878500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>881100</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1280600</v>
+      </c>
+      <c r="E9" s="3">
         <v>1177000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1135600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1069200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1083900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1108300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1128400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1116700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1177700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1238700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1359700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1367000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1379300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1371200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1231500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1020600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>988900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>859600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>878100</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>772800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>768600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>637500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>633800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>649600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>640100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>656000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>643000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>648000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>667600</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>649200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>654100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>678200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>688400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>429200</v>
+      </c>
+      <c r="E10" s="3">
         <v>387000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>345900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>311400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>333800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>313600</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>326900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>303600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>436400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>386500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>397900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>424200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>388800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>376400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>418700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>345700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>321200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>326300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>320600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>273900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>251200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>213100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>214900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>203200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>219300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>186000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>184300</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>187100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>185500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>163400</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>192500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>197200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>192700</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,8 +1218,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1321,8 +1335,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1437,110 +1454,113 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>63600</v>
+      </c>
+      <c r="E14" s="3">
         <v>5800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19900</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>16600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-31800</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-21800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>11700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-1200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>23800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>4500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>13900</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>3800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>1400</v>
       </c>
-      <c r="T14" s="3">
-        <v>0</v>
-      </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>38200</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Z14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
       <c r="AC14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="3">
         <v>12100</v>
       </c>
-      <c r="AD14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
       <c r="AF14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>54000</v>
       </c>
-      <c r="AH14" s="3" t="s">
+      <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>900</v>
       </c>
-      <c r="AJ14" s="3">
-        <v>0</v>
-      </c>
       <c r="AK14" s="3">
         <v>0</v>
       </c>
@@ -1553,124 +1573,130 @@
       <c r="AN14" s="3">
         <v>0</v>
       </c>
+      <c r="AO14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E15" s="3">
         <v>124100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>121100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>123800</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>128200</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>123600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>124600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>127500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>137900</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>126000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>122100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>116000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>117400</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>105000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>93100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>79200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>80800</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>77800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>79200</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>78500</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>96500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>85700</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>83300</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>84700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>86500</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>80400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>79500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>79200</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>85300</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>78800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>78500</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>78600</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>80800</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>77200</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>73000</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>71100</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>77500</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1708,240 +1734,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1572100</v>
+      </c>
+      <c r="E17" s="3">
         <v>1440900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1400900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1315100</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1320100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1348000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1383200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1383800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1448000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1503000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1619100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1619000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1518900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1479300</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1371600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1133400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1099000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>980300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>930400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>847200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>945500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>723100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>742400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>730000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>563200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>782200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>765300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>810800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>779400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>794000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>864000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>843600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>917300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>901900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>856800</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>846000</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>845700</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>137700</v>
+      </c>
+      <c r="E18" s="3">
         <v>123100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>80600</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>65500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>97600</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>73900</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>72100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>36500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>166100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>122200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>138500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>172100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>249200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>268300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>278600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>232900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>211100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>205600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>268300</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>199500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>74300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>127500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>106300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>122800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>296200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>59800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>62000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>24300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>73700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>18600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>31800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>35200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>34400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>38100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>32500</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>35400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1982,588 +2015,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-41100</v>
+      </c>
+      <c r="E20" s="3">
         <v>41900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>33100</v>
       </c>
-      <c r="G20" s="3">
-        <v>-35200</v>
-      </c>
       <c r="H20" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="I20" s="3">
         <v>-7700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-45700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-83500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-8600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-59600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-223000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-106200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-5900</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-2500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>600</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>-900</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>1400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>20500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>13000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>93100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>9000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3100</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>2400</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>34900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>318400</v>
+      </c>
+      <c r="E21" s="3">
         <v>205300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>208200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>156300</v>
       </c>
-      <c r="G21" s="3">
-        <v>261000</v>
-      </c>
       <c r="H21" s="3">
+        <v>273100</v>
+      </c>
+      <c r="I21" s="3">
         <v>205100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>242400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>247500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>312600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>307800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>483600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>394400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>360700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>372300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>369300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>311700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>291200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>284100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>347500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>277100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>169700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>210900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>187700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>208200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>384100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>137500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>139200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>124000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>155700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>92400</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>74000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>203500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>125000</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>114700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>113500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>102000</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>147800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>55500</v>
+      </c>
+      <c r="E22" s="3">
         <v>56900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>51900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>58000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>54900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>66800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>69200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>62900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>68500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>70300</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>70200</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>50300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>46100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>39800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>24000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15600</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15400</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>16400</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>18800</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>17900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>19100</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>18600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>19400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>20900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>19900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>20200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20100</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>23000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23100</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>22300</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>22500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>22400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>21700</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>22400</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>47900</v>
+      </c>
+      <c r="E23" s="3">
         <v>19800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-25000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>78200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>82100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>85500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>94500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>112700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>295900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>216800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>197200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>227500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>252200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>216800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>195400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>190800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>253000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>182100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>56400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>106400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>86400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>104400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>279000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>37700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>38800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>24900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>50200</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>101800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>15000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>18100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>9200</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>47900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11000</v>
+      </c>
+      <c r="E24" s="3">
         <v>-1200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4100</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-1200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-25500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-17500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>7200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-15400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>40700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>27000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>38000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>35200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>47300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26100</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>37800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>42600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>55000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>28700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>10200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>19900</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>18300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>35600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>10900</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>7800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>5300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>9700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>6300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>7700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>1800</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>6200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2678,240 +2727,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>58900</v>
+      </c>
+      <c r="E26" s="3">
         <v>21100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-23800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>103800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>19100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>81400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>87300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>128100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>255200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>189900</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>159200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>192300</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>204800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>190700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>157600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>148200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>198100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>153400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>46100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>101600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>66500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>86100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>243400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>26800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>31000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>19600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>40400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>98100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>70200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>8700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>10300</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7400</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>41700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E27" s="3">
         <v>19400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>12700</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-26200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>101900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>16900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>78900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>84500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>125000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>252400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>185800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>156600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>191100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>202000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>188100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>155800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>146800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>196600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>151800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>44700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>101100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>65400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>85500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>242600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>25700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>26300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>18000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>38900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>97300</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>69000</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7800</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>9100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>40500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3026,8 +3084,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3094,8 +3155,8 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -3112,11 +3173,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3124,11 +3185,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3142,8 +3203,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3258,8 +3322,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3374,240 +3441,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>41100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-41900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-33100</v>
       </c>
-      <c r="G32" s="3">
-        <v>35200</v>
-      </c>
       <c r="H32" s="3">
+        <v>47300</v>
+      </c>
+      <c r="I32" s="3">
         <v>7700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>45700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>83500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>8600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>59600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>223000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>106200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>5900</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>2500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-600</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>900</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>2300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>5100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>1600</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E33" s="3">
         <v>19400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>12700</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-26200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>101900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>16900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>78900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>84500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>125000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>252400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>185800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>156600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>191100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>202000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>188100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>155800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>146800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>196600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>151800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>44700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>101100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>65400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>85500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>242600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>25700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>26300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>18000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>40600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>97300</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>9100</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>40500</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3722,245 +3798,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E35" s="3">
         <v>19400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>12700</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-26200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>101900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>16900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>78900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>84500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>125000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>252400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>185800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>156600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>191100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>202000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>188100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>155800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>146800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>196600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>151800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>44700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>101100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>65400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>85500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>242600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>25700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>26300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>18000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>40600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>97300</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>9100</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>40500</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45654</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45290</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44562</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44198</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43827</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43463</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4001,8 +4086,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4043,124 +4129,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>88700</v>
+      </c>
+      <c r="E41" s="3">
         <v>91500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>94600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>81500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>76000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>114800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>121600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>145500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>126500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>119000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>111500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>132600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>127000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>126000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>146700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>99500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>68900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>67200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>77700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>71200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>81600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>65800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>76200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>76300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>72900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>69100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>87000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>95700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>107300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>81500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>104100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>122900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>106800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>110100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>124800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>138900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>114600</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4168,11 +4258,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>5100</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4275,820 +4365,844 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>651500</v>
+      </c>
+      <c r="E43" s="3">
         <v>644100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>639100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>622200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>625600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>616700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>611300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>656400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>821900</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>761300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>769300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>795900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>695200</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>687300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>602100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>542800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>470200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>482600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>436100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>388900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>409300</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>377500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>379700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>400800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>409700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>360000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>363200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>375400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>392200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>371700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>378300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>418400</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>396400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>420300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>389300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>396800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>395900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>527700</v>
+      </c>
+      <c r="E44" s="3">
         <v>622300</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>605300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>595400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>576800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>617800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>627700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>687500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>758700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>822800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>825100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>828800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>673600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>642000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>578400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>491700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>457500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>476300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>428200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>420700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>405900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>406800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>394700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>381400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>363000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>353000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>348300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>339900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>341000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>361700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>370600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>373100</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>358200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>375100</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>359600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>342100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>330800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>183600</v>
+      </c>
+      <c r="E45" s="3">
         <v>40200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>43200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>25900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>42100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>23600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>31900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>28200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>42600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>38100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>53200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>36200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>142300</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>106700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>134600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>125000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>92500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>77500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>80600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>60000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>90200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>81000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>80500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>71500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>71700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>71600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>68600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>60100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>57500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>63700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>65300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>56700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>95100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>56700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>51100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>49500</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>52000</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1553400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1502700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1495200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1454700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1439400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1496900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1507500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1619300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1855700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1843000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1876000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1902500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1638100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1562000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1461800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1259000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1089000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1103600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1022600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>940800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>987000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>931200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>931100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>930100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>917300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>853700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>867100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>871200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>897900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>878500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>918200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>971100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>956400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>962200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>924900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>927300</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>893300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2206800</v>
+      </c>
+      <c r="E47" s="3">
         <v>2324900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2162200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2111700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2263700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2332000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2415500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2378500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2251600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2164200</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2214300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2125100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>1926400</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1814600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1736200</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1563800</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1349200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1107800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1037400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>915100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>804700</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>742900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>729100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>802200</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>689400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>447700</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>458000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>433400</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>410200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>398800</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>399100</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>409100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>302000</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>290000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>279800</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>270900</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>292700</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3019800</v>
+      </c>
+      <c r="E48" s="3">
         <v>3018500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3019400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2957000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2924400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>3069700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3050800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3126200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3140700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3001700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2971100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2901800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2648200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2520800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2414500</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2033000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1995500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1995300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>2011800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1967300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>2010400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1931400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1908200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1888000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1927100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1833800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1843200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1821300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3304000</v>
+      </c>
+      <c r="E49" s="3">
         <v>3380700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3376600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3287300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3221000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3433300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3410800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3555600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3560400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3538800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3640800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3678700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2835500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2773900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2315900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1646200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1616900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1649600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1684600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1693800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1733900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1714100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1702300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="AA49" s="3">
-        <v>1749700</v>
       </c>
       <c r="AB49" s="3">
         <v>1749700</v>
       </c>
       <c r="AC49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="AD49" s="3">
         <v>1799500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5203,8 +5317,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5319,124 +5436,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>190200</v>
+      </c>
+      <c r="E52" s="3">
         <v>209800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>205300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>203100</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>199600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>222100</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>218800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>246600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>235000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>238100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>246000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>232000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>154200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>137500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>98200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>113600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>83000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>69300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>76900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>74500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>77400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>61400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>56500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>57200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>61800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>60000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>68700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>67500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>68400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>70100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>71400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>78200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>76300</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>64200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>65300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>57800</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>58600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5551,124 +5674,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10298800</v>
+      </c>
+      <c r="E54" s="3">
         <v>10452300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10275000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10032000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10070500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10572700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10620600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10942800</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>11061100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>10810300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10973200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10861100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>9202400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8808800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8026700</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6615600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6133700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>5925700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5833300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5591400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5613300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5381000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5327200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5377800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5345300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>4944900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>5036600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>4995100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5709,8 +5838,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5751,704 +5881,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>371100</v>
+      </c>
+      <c r="E57" s="3">
         <v>374800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>365700</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>348500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>348700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>331700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>349500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>343400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>425600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>394700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>427100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>433800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>472500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>398200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>414600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>351300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>307100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>272800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>264400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>245600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>255300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>207000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>197500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>211600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>239300</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>192000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>208900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>192500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>219500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>177800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>185200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>188000</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>217400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>213600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>186500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>181400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>180900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>137000</v>
+      </c>
+      <c r="E58" s="3">
         <v>144100</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>118300</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>180500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>195800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>174000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>150100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>162600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>116000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>126200</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>136500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>164200</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>69800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>63700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>32700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>35300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>24400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>55100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>41600</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>26200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>42800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>86400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>91000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>61100</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>35900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>23700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>11100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>16700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>18200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>19400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>25000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>23200</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>58600</v>
+      </c>
+      <c r="E59" s="3">
         <v>31900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>94100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>90600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>77200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>92300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>13300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>11700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>15500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>18300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>29800</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>38400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>526100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>566100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>472500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>426800</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>421200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>428200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>386200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>365100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>392400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>390400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>366000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>353800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>358100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>342800</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>321500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>330000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>313500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>297000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>290100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>302100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>325900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>314500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>283200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>245400</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>247700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1034600</v>
+      </c>
+      <c r="E60" s="3">
         <v>1010000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>996700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1035800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1043500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1062500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>963100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>967300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>998100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1033700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1013500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1099000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1068400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1028000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>919800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>813400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>752700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>756200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>692200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>637700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>675300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>623600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>606300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>651700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>688300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>595900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>566300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>546200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>540500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>485800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>482700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>506900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>559500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>546300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>489000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>451800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>451900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4024600</v>
+      </c>
+      <c r="E61" s="3">
         <v>4196200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4098500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3963300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4061300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4290300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4473600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4524200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4521300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4493000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4608000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4703200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3315000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3220900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2881100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1677900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1439000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1325700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1393800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1417500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1480500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1448000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1553100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1664900</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1558400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1559800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1640100</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1663800</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>172400</v>
+      </c>
+      <c r="E62" s="3">
         <v>186400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>183700</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>189200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>190700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>189600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>219900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>283400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>329100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>291800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>316600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>391900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>922500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>891100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>659200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>628600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>594300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>574600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>563500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>506300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>503300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>474200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>469400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>452700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>455100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>416300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>423600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>428400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>346100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>335900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>348300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>375000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>373000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>449400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>446100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>436500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>442200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6563,8 +6712,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6679,8 +6831,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6795,124 +6950,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5489300</v>
+      </c>
+      <c r="E66" s="3">
         <v>5683200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5582100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5496300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5606200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5938400</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6078000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6259800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6367400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6343400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6522700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6739500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5393300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5228600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>4533200</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3190300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2852800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2720200</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2714700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2624800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2721400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2607100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2693800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2834200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2779400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2636400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2693700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2704500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6953,8 +7114,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7069,8 +7231,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7185,8 +7350,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7301,8 +7469,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7417,124 +7588,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4074900</v>
+      </c>
+      <c r="E72" s="3">
         <v>4018000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3998600</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3986000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4012100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3910200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3893300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3814400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3733300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3648700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3523700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3271300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3085500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>2929000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2737900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2535900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2347800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2192100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2045300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1848700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1696900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1652200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1551100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1485600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1400100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1157500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1131800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1105500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>981200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>875500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>867700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>858600</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>852800</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7649,8 +7826,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7765,8 +7945,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7881,124 +8064,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4736900</v>
+      </c>
+      <c r="E76" s="3">
         <v>4688800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4613100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4448400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4377800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4551400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4460900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4593100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4605400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4380700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4368200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4032500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>3809000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3580100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3493500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3425300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3281000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3205500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3118600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>2966600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2891900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2773900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2633400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2543600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2565800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2308500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2342900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2290500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8113,245 +8302,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46025</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45654</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45290</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44562</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44198</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43827</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43463</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43099</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>56900</v>
+      </c>
+      <c r="E81" s="3">
         <v>19400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>12700</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-26200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>101900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>16900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>78900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>84500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>125000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>252400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>185800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>156600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>191100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>202000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>188100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>155800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>146800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>196600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>151800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>44700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>101100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>65400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>85500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>242600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>25700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>26300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>18000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>40600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>97300</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>105700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>9100</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>40500</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8392,124 +8590,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>100300</v>
+      </c>
+      <c r="E83" s="3">
         <v>95700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>96200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>99500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>104800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>93800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>88700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>89900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>91500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>79700</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>72100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>62700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>117400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>105000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>93100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>79200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>80800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>77800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>79200</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>78500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>96500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>85700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>83300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>84700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>86500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>80400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>79500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>79200</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>85300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>78800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>78500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>78600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>80800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>77200</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>73000</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>71100</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>77500</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8624,8 +8826,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8740,8 +8945,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8856,8 +9064,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8972,8 +9183,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9088,124 +9302,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>440600</v>
+      </c>
+      <c r="E89" s="3">
         <v>224300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>145800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>249000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>154400</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>274500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>146500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>263900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>217000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>276600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>217300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>188400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>175300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>277400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>208800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>152200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>252400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>154100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>159100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>138800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>154200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>206800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>229100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>34500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>99900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>108400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>105700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>48600</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>198900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>71700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>101100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>26900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>141800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>71200</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>103100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>94500</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>110500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9246,124 +9466,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-156400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-71000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-63000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-73300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-67400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-98000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-93800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-174900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-146200</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-123000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-111300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-134200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-105600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-79900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-71600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-82400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-65600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-65300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-60800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-95200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="Y91" s="3">
-        <v>-61600</v>
       </c>
       <c r="Z91" s="3">
         <v>-61600</v>
       </c>
       <c r="AA91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-114400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-77200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-84300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9478,8 +9702,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9594,124 +9821,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-234600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-287500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-108700</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-50700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-46300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-64900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-96700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-291000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-168800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-158300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-91600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-193800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-598000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-294500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-270500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-89800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-65600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-64300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-123300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-64600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9752,8 +9985,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9790,8 +10024,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9868,8 +10102,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9984,8 +10221,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10100,8 +10340,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10216,352 +10459,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-208200</v>
+      </c>
+      <c r="E100" s="3">
         <v>47200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-30500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-185200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-166300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-201000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-81000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>48800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-25900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-117900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-152700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1172800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-4300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>325300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1176700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>180900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>18700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-69200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-89800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-81000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-19500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-159500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-168400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>40400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>5300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-49200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-32100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>21200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>46200</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>14600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-13100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>6500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-11400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>9000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>7300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>25600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4200</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>25600</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-4200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-8100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>1200</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-5600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>2900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3800</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>3900</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>300</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1700</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>700</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>5100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>5400</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>10900</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>300</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-14500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>6900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-43600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-4700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-27000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>28200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>10900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>9400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-17700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>111700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>47300</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>30500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-10600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-10300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>15800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>25800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>16100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>24300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-9200</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/DAR_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>DAR</t>
   </si>
@@ -656,528 +656,540 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="24" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="25" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="2">
         <v>46025</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45654</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45290</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44562</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44198</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43827</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43463</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43099</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1550800</v>
+      </c>
+      <c r="E8" s="3">
         <v>1709800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1564000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1481500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1380600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1417700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1421900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1455300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>1420300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>1614100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1625200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1757600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1791200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1768100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1747600</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1650200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1366300</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1310100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>1185900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1198700</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1046700</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1019800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>850600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>848700</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>852800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>859400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>842000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>827300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>835100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>853100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>812600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>846600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>875400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>952500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>936300</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>894900</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>878500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>881100</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>853900</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1145900</v>
+      </c>
+      <c r="E9" s="3">
         <v>1280600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1177000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1135600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1069200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1083900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1108300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1128400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1116700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1177700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1238700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1359700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1367000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1379300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1371200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1231500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1020600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>988900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>859600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>878100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>772800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>768600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>637500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>633800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>649600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>640100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>656000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>643000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>648000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>667600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>649200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>654100</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>678200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1489000</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1489500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1401200</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1378500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>688400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>671200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>404900</v>
+      </c>
+      <c r="E10" s="3">
         <v>429200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>387000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>345900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>311400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>333800</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>313600</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>326900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>303600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>436400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>386500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>397900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>424200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>388800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>376400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>418700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>345700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>321200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>326300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>320600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>273900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>251200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>213100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>214900</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>203200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>219300</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>186000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>184300</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>187100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>185500</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>163400</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>192500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>197200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>-536500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>-553200</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>-506300</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>-500000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>192700</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>182700</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1219,8 +1231,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1338,8 +1351,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1457,113 +1473,116 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E14" s="3">
         <v>63600</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>5800</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19900</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-300</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>16600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-31800</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-21800</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>11700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-1200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>-4600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>23800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>4500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>13900</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1400</v>
       </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
       <c r="V14" s="3">
         <v>0</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
         <v>800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>38200</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
+      <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC14" s="3">
-        <v>0</v>
-      </c>
       <c r="AD14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="3">
         <v>12100</v>
       </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
       <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>54000</v>
       </c>
-      <c r="AI14" s="3" t="s">
+      <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>900</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
-      </c>
       <c r="AL14" s="3">
         <v>0</v>
       </c>
@@ -1576,127 +1595,133 @@
       <c r="AO14" s="3">
         <v>0</v>
       </c>
+      <c r="AP14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>130900</v>
+      </c>
+      <c r="E15" s="3">
         <v>139500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>124100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>121100</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>123800</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>128200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>123600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>124600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>127500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>137900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>126000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>122100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>116000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>117400</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>105000</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>93100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>79200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>80800</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>77800</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>79200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>78500</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>96500</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>85700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>83300</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>84700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>86500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>80400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>79500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>79200</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>85300</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>78800</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>78500</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>78600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>80800</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>77200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>73000</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>71100</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>77500</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1735,246 +1760,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>1425900</v>
+      </c>
+      <c r="E17" s="3">
         <v>1572100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1440900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1400900</v>
       </c>
-      <c r="G17" s="3">
-        <v>1315100</v>
-      </c>
       <c r="H17" s="3">
+        <v>1314600</v>
+      </c>
+      <c r="I17" s="3">
         <v>1320100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>1348000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>1383200</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>1383800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>1448000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1503000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1619100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1619000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>1518900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1479300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1371600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1133400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1099000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>980300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>930400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>847200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>945500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>723100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>742400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>730000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>563200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>782200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>765300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>810800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>779400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>794000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>864000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>843600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>917300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>901900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>856800</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>846000</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>845700</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>818300</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>124900</v>
+      </c>
+      <c r="E18" s="3">
         <v>137700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>123100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>80600</v>
       </c>
-      <c r="G18" s="3">
-        <v>65500</v>
-      </c>
       <c r="H18" s="3">
+        <v>66000</v>
+      </c>
+      <c r="I18" s="3">
         <v>97600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>73900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>72100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>36500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>166100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>122200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>138500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>172100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>249200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>268300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>278600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>232900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>211100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>205600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>268300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>199500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>74300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>127500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>106300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>122800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>296200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>59800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>62000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>24300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>73700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>18600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-17400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>31800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>35200</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>34400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>38100</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>32500</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>35400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>35600</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2016,603 +2048,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-110400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-41100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>41900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-6500</v>
       </c>
-      <c r="G20" s="3">
-        <v>33100</v>
-      </c>
       <c r="H20" s="3">
+        <v>25900</v>
+      </c>
+      <c r="I20" s="3">
         <v>-47300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-7700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-45700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-83500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-59600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-223000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-106200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-5900</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>600</v>
       </c>
-      <c r="V20" s="3">
-        <v>0</v>
-      </c>
       <c r="W20" s="3">
+        <v>0</v>
+      </c>
+      <c r="X20" s="3">
         <v>-900</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>1400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>20500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>13000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>93100</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>9000</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3100</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-1600</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>34900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>16400</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>366200</v>
+      </c>
+      <c r="E21" s="3">
         <v>318400</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>205300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>208200</v>
       </c>
-      <c r="G21" s="3">
-        <v>156300</v>
-      </c>
       <c r="H21" s="3">
+        <v>163900</v>
+      </c>
+      <c r="I21" s="3">
         <v>273100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>205100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>242400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>247500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>312600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>307800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>483600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>394400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>360700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>372300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>369300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>311700</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>291200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>284100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>347500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>277100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>169700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>210900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>187700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>208200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>384100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>137500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>139200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>124000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>155700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>92400</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>74000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>203500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>125000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>114700</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>113500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>102000</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>147800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>122700</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>54100</v>
+      </c>
+      <c r="E22" s="3">
         <v>55500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>56900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>51900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>58000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>54900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>66800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>69200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>62900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>68500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>70300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>70200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>50300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>46100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>39800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>24000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15600</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>15300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>16400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>16900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>18800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>17900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>19100</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>18600</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>19400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>20900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>19900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>20200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>20100</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>23000</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>23100</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>22300</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>22500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>22400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>21700</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>22400</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>23900</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>175700</v>
+      </c>
+      <c r="E23" s="3">
         <v>47900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-25000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>78200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>82100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>85500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>94500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>112700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>295900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>216800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>197200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>227500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>252200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>216800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>195400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>190800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>253000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>182100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>56400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>106400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>86400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>104400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>279000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>37700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>38800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>24900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>50200</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-6500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-27500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>101800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>21900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>15000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>18100</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>9200</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>47900</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>28100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-1200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>4100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-1200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-25500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-17500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>7200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-15400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>40700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>27000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>38000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>35200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>47300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26100</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>37800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>42600</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>55000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>28700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>10200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>19900</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>18300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>35600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>10900</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>7800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>5300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>9700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-48300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>6300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>7700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>6200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-700</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2730,246 +2778,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>137100</v>
+      </c>
+      <c r="E26" s="3">
         <v>58900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>21100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-23800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>103800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>87300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>128100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>255200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>189900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>159200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>192300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>204800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>190700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>157600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>148200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>198100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>153400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>46100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>101600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>66500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>86100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>243400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>26800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>31000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>19600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>40400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-29100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>98100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>70200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>8700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>10300</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>7400</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>41700</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>28900</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E27" s="3">
         <v>56900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>19400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>12700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-26200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>101900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>16900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>78900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>84500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>125000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>252400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>185800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>156600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>191100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>202000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>188100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>155800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>146800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>196600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>151800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>44700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>101100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>65400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>85500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>242600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>25700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>26300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>18000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>38900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>97300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>69000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>7800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>9100</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>5800</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>40500</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3087,8 +3144,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3158,8 +3218,8 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -3176,11 +3236,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>1700</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3188,11 +3248,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>36700</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3206,8 +3266,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3325,8 +3388,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3444,246 +3510,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>110400</v>
+      </c>
+      <c r="E32" s="3">
         <v>41100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-41900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>6500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-33100</v>
-      </c>
       <c r="H32" s="3">
+        <v>-25900</v>
+      </c>
+      <c r="I32" s="3">
         <v>47300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>7700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>45700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>83500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>59600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>223000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>106200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>5900</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-600</v>
       </c>
-      <c r="V32" s="3">
-        <v>0</v>
-      </c>
       <c r="W32" s="3">
+        <v>0</v>
+      </c>
+      <c r="X32" s="3">
         <v>900</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-20500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>5100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-13000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-93100</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-9000</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3100</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>1600</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-34900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>-16400</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E33" s="3">
         <v>56900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>19400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>12700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-26200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>101900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>16900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>78900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>84500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>125000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>252400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>185800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>156600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>191100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>202000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>188100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>155800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>146800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>196600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>151800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>44700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>101100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>65400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>85500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>242600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>25700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>26300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>18000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>40600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>97300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>105700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>7800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>9100</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>5800</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>40500</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3801,251 +3876,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E35" s="3">
         <v>56900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>19400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>12700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-26200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>101900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>16900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>78900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>84500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>125000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>252400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>185800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>156600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>191100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>202000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>188100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>155800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>146800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>196600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>151800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>44700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>101100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>65400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>85500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>242600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>25700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>26300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>18000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>40600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>97300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>105700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>7800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>9100</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>5800</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>40500</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E38" s="2">
         <v>46025</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45654</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45290</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44562</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44198</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43827</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43463</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43099</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4087,8 +4171,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4130,127 +4215,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>116000</v>
+      </c>
+      <c r="E41" s="3">
         <v>88700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>91500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>94600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>81500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>76000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>114800</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>121600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>145500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>126500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>119000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>111500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>132600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>127000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>126000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>146700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>99500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>68900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>67200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>77700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>71200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>81600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>65800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>76200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>76300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>72900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>69100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>87000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>95700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>107300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>81500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>104100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>122900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>106800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>110100</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>124800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>138900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>114600</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>148600</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4261,11 +4350,11 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>5100</v>
       </c>
-      <c r="G42" s="3">
-        <v>0</v>
-      </c>
       <c r="H42" s="3">
         <v>0</v>
       </c>
@@ -4368,841 +4457,865 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>644300</v>
+      </c>
+      <c r="E43" s="3">
         <v>651500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>644100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>639100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>622200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>625600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>616700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>611300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>656400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>821900</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>761300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>769300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>795900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>695200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>687300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>602100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>542800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>470200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>482600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>436100</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>388900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>409300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>377500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>379700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>400800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>409700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>360000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>363200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>375400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>392200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>371700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>378300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>418400</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>396400</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>420300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>389300</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>396800</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>395900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>396100</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>577600</v>
+      </c>
+      <c r="E44" s="3">
         <v>527700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>622300</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>605300</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>595400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>576800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>617800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>627700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>687500</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>758700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>822800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>825100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>828800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>673600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>642000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>578400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>491700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>457500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>476300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>428200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>420700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>405900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>406800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>394700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>381400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>363000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>353000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>348300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>339900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>341000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>361700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>370600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>373100</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>358200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>375100</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>359600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>342100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>330800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>359100</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>189100</v>
+      </c>
+      <c r="E45" s="3">
         <v>183600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>40200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>43200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>25900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>42100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>23600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>31900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>28200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>42600</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>38100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>53200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>36200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>142300</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>106700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>134600</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>125000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>92500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>77500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>80600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>60000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>90200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>81000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>80500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>71500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>71700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>71600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>68600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>60100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>57500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>63700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>65300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>56700</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>95100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>56700</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>51100</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>49500</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>52000</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>59200</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1646200</v>
+      </c>
+      <c r="E46" s="3">
         <v>1553400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1502700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1495200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1454700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1439400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>1496900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>1507500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>1619300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1855700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>1843000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>1876000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>1902500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>1638100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>1562000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>1461800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>1259000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>1089000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>1103600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>1022600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>940800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>987000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>931200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>931100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>930100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>917300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>853700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>867100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>871200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>897900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>878500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>918200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>971100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>956400</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>962200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>924900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>927300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>893300</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>963000</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2444900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2206800</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2324900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2162200</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>2111700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2263700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2332000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>2415500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>2378500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>2251600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>2164200</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>2214300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>2125100</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>1926400</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>1814600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>1736200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>1563800</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>1349200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>1107800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>1037400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>915100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>804700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>742900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>729100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>802200</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>689400</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>447700</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>458000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>433400</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>410200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>398800</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>399100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>409100</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>302000</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>290000</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>279800</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>270900</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>292700</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>261700</v>
       </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>3006400</v>
+      </c>
+      <c r="E48" s="3">
         <v>3019800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>3018500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>3019400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2957000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2924400</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>3069700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>3050800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>3126200</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>3140700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>3001700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2971100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>2901800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>2648200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>2520800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>2414500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>2033000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1995500</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1995300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>2011800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1967300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>2010400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1931400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1908200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1888000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1927100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1833800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1843200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1821300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1687900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1631000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1624400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1657600</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>1645800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>1621900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>1584700</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>1532600</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>1515600</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>1535200</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3320300</v>
+      </c>
+      <c r="E49" s="3">
         <v>3304000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>3380700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>3376600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>3287300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3221000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3433300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3410800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3555600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3560400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3538800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3640800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3678700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2835500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2773900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2315900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1646200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1616900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1649600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1684600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1693800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1733900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1714100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1702300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1700400</v>
-      </c>
-      <c r="AB49" s="3">
-        <v>1749700</v>
       </c>
       <c r="AC49" s="3">
         <v>1749700</v>
       </c>
       <c r="AD49" s="3">
+        <v>1749700</v>
+      </c>
+      <c r="AE49" s="3">
         <v>1799500</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1801700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1825000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1826800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1843800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1969500</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>1977600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>1996200</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>1975100</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>1931100</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>1937800</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>2003900</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5320,8 +5433,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5439,127 +5555,133 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E52" s="3">
         <v>190200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>209800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>205300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>203100</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>199600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>222100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>218800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>246600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>235000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>238100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>246000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>232000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>154200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>137500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>98200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>113600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>83000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>69300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>76900</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>74500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>77400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>61400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>56500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>57200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>61800</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>60000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>68700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>67500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>68400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>70100</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>71400</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>78200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>76300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>64200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>65300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>57800</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>58600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5677,127 +5799,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>10641100</v>
+      </c>
+      <c r="E54" s="3">
         <v>10298800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>10452300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>10275000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>10032000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>10070500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>10572700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>10620600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>10942800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>11061100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>10810300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>10973200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>10861100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>9202400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>8808800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>8026700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6615600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6133700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>5925700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>5833300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>5591400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>5613300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>5381000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>5327200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>5377800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>5345300</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>4944900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5036600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>4995100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4889400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>4805200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>4856900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5085500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4958200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>4934500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>4829900</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4719700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4698000</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>4816900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5839,8 +5967,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5882,722 +6011,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>356200</v>
+      </c>
+      <c r="E57" s="3">
         <v>371100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>374800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>365700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>348500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>348700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>331700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>349500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>343400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>425600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>394700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>427100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>433800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>472500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>398200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>414600</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>351300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>307100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>272800</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>264400</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>245600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>255300</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>207000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>197500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>211600</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>239300</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>192000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>208900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>192500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>219500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>177800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>185200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>188000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>217400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>213600</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>186500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>181400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>180900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>168600</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>137900</v>
+      </c>
+      <c r="E58" s="3">
         <v>137000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>144100</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>118300</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>180500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>195800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>174000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>150100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>162600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>116000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>126200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>136500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>164200</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>69800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>63700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>32700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>35300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>24400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>55100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>41600</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>27500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>26200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>42800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>86400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>91000</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>61100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>35900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>23700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7500</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>11100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>16700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>16100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>18200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>19400</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>25000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>23200</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>27200</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>70500</v>
+      </c>
+      <c r="E59" s="3">
         <v>58600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>94100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>90600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>77200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>92300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>13300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>11700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>15500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>29800</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>38400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>526100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>566100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>472500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>426800</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>421200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>428200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>386200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>365100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>392400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>390400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>366000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>353800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>358100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>342800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>321500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>330000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>313500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>297000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>290100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>302100</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>325900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>314500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>283200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>245400</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>247700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>263900</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1039800</v>
+      </c>
+      <c r="E60" s="3">
         <v>1034600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1010000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>996700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1035800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1043500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1062500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>963100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>967300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>998100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>1033700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1013500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1099000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1068400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1028000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>919800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>813400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>752700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>756200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>692200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>637700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>675300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>623600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>606300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>651700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>688300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>595900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>566300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>546200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>540500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>485800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>482700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>506900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>559500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>546300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>489000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>451800</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>451900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>459700</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4209200</v>
+      </c>
+      <c r="E61" s="3">
         <v>4024600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4196200</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4098500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3963300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>4061300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4290300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4473600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4524200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>4521300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>4493000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>4608000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>4703200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3315000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3220900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2881100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1677900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1439000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1325700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1393800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1417500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1480500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1448000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1553100</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1664900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1558400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1559800</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1640100</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1663800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1666900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1668100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1687800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1764400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1698100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1734200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1727600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1727500</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1727700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1818400</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>161400</v>
+      </c>
+      <c r="E62" s="3">
         <v>172400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>186400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>183700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>189200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>190700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>189600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>219900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>283400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>329100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>291800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>316600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>391900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>922500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>891100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>659200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>628600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>594300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>574600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>563500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>506300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>503300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>474200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>469400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>452700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>455100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>416300</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>423600</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>428400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>346100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>335900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>348300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>375000</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>373000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>449400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>446100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>436500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>442200</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>453500</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6715,8 +6863,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6834,8 +6985,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6953,127 +7107,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5696800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5489300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5683200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5582100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5496300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5606200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5938400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6078000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6259800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6367400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6343400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6522700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6739500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5393300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5228600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>4533200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3190300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2852800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>2720200</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>2714700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>2624800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>2721400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>2607100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>2693800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>2834200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>2779400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>2636400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>2693700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>2704500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>2616300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>2550800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>2593500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>2720100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>2713300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>2811900</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>2765600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>2720300</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2725000</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>2833200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7115,8 +7275,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7234,8 +7395,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7353,8 +7517,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7472,8 +7639,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7591,127 +7761,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>4209300</v>
+      </c>
+      <c r="E72" s="3">
         <v>4074900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>4018000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3998600</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3986000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4012100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3910200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3893300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3814400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>3733300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>3648700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3523700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3271300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3085500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>2929000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>2737900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>2535900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>2347800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>2192100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>2045300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1848700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1696900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1652200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1551100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1485600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1400100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1157500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1131800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1105500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1087500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>1046900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>1052900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>1083300</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>981200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>875500</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>867700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>858600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>852800</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>812300</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7829,8 +8005,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7948,8 +8127,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8067,127 +8249,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>4876100</v>
+      </c>
+      <c r="E76" s="3">
         <v>4736900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>4688800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>4613100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>4448400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>4377800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>4551400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>4460900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>4593100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>4605400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4380700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4368200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4032500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>3809000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>3580100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>3493500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>3425300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3281000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3205500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3118600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2966600</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2891900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2773900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2633400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2543600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2565800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2308500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>2342900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>2290500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>2273000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>2254400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>2263400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>2365400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>2244900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>2122700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>2064300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1999400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1973000</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1983700</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8305,251 +8493,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="2">
         <v>46025</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45654</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45290</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44562</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44198</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43827</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43463</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43099</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>134300</v>
+      </c>
+      <c r="E81" s="3">
         <v>56900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>19400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>12700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-26200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>101900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>16900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>78900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>84500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>125000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>252400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>185800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>156600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>191100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>202000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>188100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>155800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>146800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>196600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>151800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>44700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>101100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>65400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>85500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>242600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>25700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>26300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>18000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>40600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-6000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-30400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>97300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>105700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>7800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>9100</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>5800</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>40500</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>28700</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8591,127 +8788,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>98500</v>
+      </c>
+      <c r="E83" s="3">
         <v>100300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>95700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>96200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>99500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>104800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>93800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>88700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>89900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>91500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>79700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>72100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>62700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>117400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>105000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>93100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>79200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>80800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>77800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>79200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>78500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>96500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>85700</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>83300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>84700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>86500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>80400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>79500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>79200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>85300</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>78800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>78500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>78600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>80800</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>77200</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>73000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>71100</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>77500</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>70700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8829,8 +9030,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8948,8 +9152,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9067,8 +9274,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9186,8 +9396,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9305,127 +9518,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>153000</v>
+      </c>
+      <c r="E89" s="3">
         <v>440600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>224300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>145800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>249000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>154400</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>274500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>146500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>263900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>217000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>276600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>217300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>188400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>175300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>277400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>208800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>152200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>252400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>154100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>159100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>138800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>154200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>206800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>229100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>34500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>99900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>108400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>105700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>48600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>198900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>71700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>101100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>26900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>141800</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>71200</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>103100</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>94500</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>110500</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>112300</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9467,127 +9686,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-94800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-156400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90100</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-71000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-63000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-73300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-67400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-98000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-93800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-174900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-146200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-123000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-111300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-134200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-105600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-79900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-71600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-82400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-65600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-65300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-60800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-95200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61700</v>
-      </c>
-      <c r="Z91" s="3">
-        <v>-61600</v>
       </c>
       <c r="AA91" s="3">
         <v>-61600</v>
       </c>
       <c r="AB91" s="3">
+        <v>-61600</v>
+      </c>
+      <c r="AC91" s="3">
         <v>-114400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-77200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-83600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-84300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-108200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-74600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-82500</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-56600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-77700</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-68600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-65500</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-75300</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-58800</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9705,8 +9928,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9824,127 +10050,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-288700</v>
+      </c>
+      <c r="E94" s="3">
         <v>-234600</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-287500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-108700</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-50700</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-46300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-64900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-96700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-291000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-168800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-158300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-91600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1256800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-193800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-598000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-1330300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-294500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-270500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-89800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-65600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-123300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-61500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-61200</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-64600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-103200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-72100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-83000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-79800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-153600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-78200</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-55400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-55300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-73300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-70500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-80300</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-59900</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-72500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-56700</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9986,8 +10218,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10027,8 +10260,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10105,8 +10338,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10224,8 +10460,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10343,8 +10582,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10462,361 +10704,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>183100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-208200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>47200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-30500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-185200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-166300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-201000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-81000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>48800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-25900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-117900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-152700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1172800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>325300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1176700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>180900</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>18700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-69200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-89800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-81000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-19500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-159500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-168400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>40400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>5300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-49200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-32100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>21200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-17600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-21300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-54800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>46200</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-75700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-20800</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-47800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-10600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-66700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-61900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-6200</v>
+      </c>
+      <c r="E101" s="3">
         <v>14600</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-13100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>6500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-11400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>9000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>9300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>25600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4200</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-8100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>25600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-4200</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-8100</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>1200</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-5600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>2900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>3900</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-6900</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1700</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>700</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1600</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>5100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-1700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>3900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>5400</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>10900</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>300</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>-5400</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2900</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>24700</v>
+      </c>
+      <c r="E102" s="3">
         <v>-700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-14500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>6900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-43600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-4700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-27000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>28200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>10900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>9400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-17700</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>111700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>47300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>30500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-10600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-10300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>15800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-17800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-8700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-11500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>25800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-22700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-18700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>16100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-3400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-14700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-14100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>24300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-34000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-9200</v>
       </c>
     </row>
